--- a/application/controllers/dedform/DED-MDS/04X-09C.xlsx
+++ b/application/controllers/dedform/DED-MDS/04X-09C.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\src\form\application\controllers\dedform\DED-MDS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{566915EF-CA6A-473B-8B09-4A2125185637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF731540-4A8E-48C9-BD0C-765FCF5CE45D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="2220" windowWidth="29040" windowHeight="15720" tabRatio="684" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="684" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="10X-03C" sheetId="1" r:id="rId1"/>
@@ -629,7 +629,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="191">
   <si>
     <t>Dated</t>
   </si>
@@ -1259,6 +1259,15 @@
   <si>
     <t>USER</t>
   </si>
+  <si>
+    <t>D/E DEM</t>
+  </si>
+  <si>
+    <t>D/E DDEM</t>
+  </si>
+  <si>
+    <t>PREPARED</t>
+  </si>
 </sst>
 </file>
 
@@ -1268,7 +1277,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="[$-409]dd\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="61" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="Arial"/>
@@ -1621,6 +1630,17 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="20"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="23">
     <fill>
@@ -2491,7 +2511,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="287">
+  <cellXfs count="295">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2958,6 +2978,24 @@
     <xf numFmtId="165" fontId="23" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="60" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="59" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="18" fillId="2" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3207,33 +3245,6 @@
     <xf numFmtId="164" fontId="18" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="34" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="34" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="34" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="34" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="34" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="34" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="34" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="34" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="18" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3309,16 +3320,49 @@
     <xf numFmtId="164" fontId="19" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="60" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="60" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="60" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="60" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="60" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="60" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="59" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="59" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="59" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="59" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="59" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="59" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="59" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="59" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="59" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4569,15 +4613,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:175" ht="32.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="AD1" s="249"/>
-      <c r="AE1" s="250"/>
-      <c r="AF1" s="251"/>
-      <c r="AG1" s="249"/>
-      <c r="AH1" s="250"/>
-      <c r="AI1" s="251"/>
-      <c r="AJ1" s="249"/>
-      <c r="AK1" s="250"/>
-      <c r="AL1" s="251"/>
+      <c r="AD1" s="280" t="s">
+        <v>188</v>
+      </c>
+      <c r="AE1" s="281"/>
+      <c r="AF1" s="282"/>
+      <c r="AG1" s="170" t="s">
+        <v>189</v>
+      </c>
+      <c r="AH1" s="170"/>
+      <c r="AI1" s="170"/>
+      <c r="AJ1" s="170" t="s">
+        <v>190</v>
+      </c>
+      <c r="AK1" s="170"/>
+      <c r="AL1" s="170"/>
     </row>
     <row r="2" spans="1:175" ht="32.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
@@ -4588,23 +4638,23 @@
       <c r="D2" s="6"/>
       <c r="E2" s="20"/>
       <c r="F2" s="20"/>
-      <c r="G2" s="262" t="s">
+      <c r="G2" s="259" t="s">
         <v>177</v>
       </c>
-      <c r="H2" s="263"/>
-      <c r="I2" s="263"/>
-      <c r="J2" s="263"/>
-      <c r="K2" s="263"/>
-      <c r="L2" s="263"/>
-      <c r="M2" s="263"/>
-      <c r="N2" s="263"/>
-      <c r="O2" s="263"/>
-      <c r="P2" s="263"/>
-      <c r="Q2" s="263"/>
-      <c r="R2" s="263"/>
-      <c r="S2" s="263"/>
-      <c r="T2" s="263"/>
-      <c r="U2" s="264"/>
+      <c r="H2" s="260"/>
+      <c r="I2" s="260"/>
+      <c r="J2" s="260"/>
+      <c r="K2" s="260"/>
+      <c r="L2" s="260"/>
+      <c r="M2" s="260"/>
+      <c r="N2" s="260"/>
+      <c r="O2" s="260"/>
+      <c r="P2" s="260"/>
+      <c r="Q2" s="260"/>
+      <c r="R2" s="260"/>
+      <c r="S2" s="260"/>
+      <c r="T2" s="260"/>
+      <c r="U2" s="261"/>
       <c r="Y2" s="57" t="s">
         <v>26</v>
       </c>
@@ -4617,134 +4667,134 @@
       <c r="AB2" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="AD2" s="252"/>
-      <c r="AE2" s="253"/>
-      <c r="AF2" s="254"/>
-      <c r="AG2" s="252"/>
-      <c r="AH2" s="253"/>
-      <c r="AI2" s="254"/>
-      <c r="AJ2" s="252"/>
-      <c r="AK2" s="253"/>
-      <c r="AL2" s="254"/>
-      <c r="AM2" s="261"/>
-      <c r="AN2" s="261"/>
-      <c r="AO2" s="261"/>
-      <c r="AP2" s="261"/>
-      <c r="AQ2" s="261"/>
-      <c r="AR2" s="261"/>
-      <c r="AS2" s="261"/>
-      <c r="AT2" s="261"/>
-      <c r="AU2" s="261"/>
-      <c r="AV2" s="261"/>
-      <c r="AW2" s="261"/>
-      <c r="AX2" s="261"/>
-      <c r="AY2" s="261"/>
-      <c r="AZ2" s="261"/>
-      <c r="BA2" s="261"/>
-      <c r="BB2" s="261"/>
-      <c r="BC2" s="261"/>
-      <c r="BD2" s="261"/>
-      <c r="BE2" s="261"/>
-      <c r="BF2" s="261"/>
-      <c r="BG2" s="261"/>
-      <c r="BH2" s="261"/>
-      <c r="BI2" s="261"/>
-      <c r="BJ2" s="261"/>
-      <c r="BK2" s="261"/>
-      <c r="BL2" s="261"/>
-      <c r="BM2" s="261"/>
-      <c r="BN2" s="261"/>
-      <c r="BO2" s="261"/>
-      <c r="BP2" s="261"/>
-      <c r="BQ2" s="261"/>
-      <c r="BR2" s="261"/>
-      <c r="BS2" s="261"/>
-      <c r="BT2" s="261"/>
-      <c r="BU2" s="261"/>
-      <c r="BV2" s="261"/>
-      <c r="BW2" s="261"/>
-      <c r="BX2" s="261"/>
-      <c r="BY2" s="261"/>
-      <c r="BZ2" s="261"/>
-      <c r="CA2" s="261"/>
-      <c r="CB2" s="261"/>
-      <c r="CC2" s="261"/>
-      <c r="CD2" s="261"/>
-      <c r="CE2" s="261"/>
-      <c r="CF2" s="261"/>
-      <c r="CG2" s="261"/>
-      <c r="CH2" s="261"/>
-      <c r="CI2" s="261"/>
-      <c r="CJ2" s="261"/>
-      <c r="CK2" s="261"/>
-      <c r="CL2" s="261"/>
-      <c r="CM2" s="261"/>
-      <c r="CN2" s="261"/>
-      <c r="CO2" s="261"/>
-      <c r="CP2" s="261"/>
-      <c r="CQ2" s="261"/>
-      <c r="CR2" s="261"/>
-      <c r="CS2" s="261"/>
-      <c r="CT2" s="261"/>
-      <c r="CU2" s="261"/>
-      <c r="CV2" s="261"/>
-      <c r="CW2" s="261"/>
-      <c r="CX2" s="261"/>
-      <c r="CY2" s="261"/>
-      <c r="CZ2" s="261"/>
-      <c r="DA2" s="261"/>
-      <c r="DB2" s="261"/>
-      <c r="DC2" s="261"/>
-      <c r="DD2" s="261"/>
-      <c r="DE2" s="261"/>
-      <c r="DF2" s="261"/>
-      <c r="DG2" s="261"/>
-      <c r="DH2" s="261"/>
-      <c r="DI2" s="261"/>
-      <c r="DJ2" s="261"/>
-      <c r="DK2" s="261"/>
-      <c r="DL2" s="261"/>
-      <c r="DM2" s="261"/>
-      <c r="DN2" s="261"/>
-      <c r="DO2" s="261"/>
-      <c r="DP2" s="261"/>
-      <c r="DQ2" s="261"/>
-      <c r="DR2" s="261"/>
-      <c r="DS2" s="261"/>
-      <c r="DT2" s="261"/>
-      <c r="DU2" s="261"/>
-      <c r="DV2" s="261"/>
-      <c r="DW2" s="261"/>
-      <c r="DX2" s="261"/>
-      <c r="DY2" s="261"/>
-      <c r="DZ2" s="261"/>
-      <c r="EA2" s="261"/>
-      <c r="EB2" s="261"/>
-      <c r="EC2" s="261"/>
-      <c r="ED2" s="261"/>
-      <c r="EE2" s="261"/>
-      <c r="EF2" s="261"/>
-      <c r="EG2" s="261"/>
-      <c r="EH2" s="261"/>
-      <c r="EI2" s="261"/>
-      <c r="EJ2" s="261"/>
-      <c r="EK2" s="261"/>
-      <c r="EL2" s="261"/>
-      <c r="EM2" s="261"/>
-      <c r="EN2" s="261"/>
-      <c r="EO2" s="261"/>
-      <c r="EP2" s="261"/>
-      <c r="EQ2" s="261"/>
-      <c r="ER2" s="261"/>
-      <c r="ES2" s="261"/>
-      <c r="ET2" s="261"/>
-      <c r="EU2" s="261"/>
-      <c r="EV2" s="261"/>
-      <c r="EW2" s="261"/>
-      <c r="EX2" s="261"/>
-      <c r="EY2" s="261"/>
-      <c r="EZ2" s="261"/>
-      <c r="FA2" s="261"/>
+      <c r="AD2" s="283"/>
+      <c r="AE2" s="284"/>
+      <c r="AF2" s="285"/>
+      <c r="AG2" s="170"/>
+      <c r="AH2" s="170"/>
+      <c r="AI2" s="170"/>
+      <c r="AJ2" s="170"/>
+      <c r="AK2" s="170"/>
+      <c r="AL2" s="170"/>
+      <c r="AM2" s="258"/>
+      <c r="AN2" s="258"/>
+      <c r="AO2" s="258"/>
+      <c r="AP2" s="258"/>
+      <c r="AQ2" s="258"/>
+      <c r="AR2" s="258"/>
+      <c r="AS2" s="258"/>
+      <c r="AT2" s="258"/>
+      <c r="AU2" s="258"/>
+      <c r="AV2" s="258"/>
+      <c r="AW2" s="258"/>
+      <c r="AX2" s="258"/>
+      <c r="AY2" s="258"/>
+      <c r="AZ2" s="258"/>
+      <c r="BA2" s="258"/>
+      <c r="BB2" s="258"/>
+      <c r="BC2" s="258"/>
+      <c r="BD2" s="258"/>
+      <c r="BE2" s="258"/>
+      <c r="BF2" s="258"/>
+      <c r="BG2" s="258"/>
+      <c r="BH2" s="258"/>
+      <c r="BI2" s="258"/>
+      <c r="BJ2" s="258"/>
+      <c r="BK2" s="258"/>
+      <c r="BL2" s="258"/>
+      <c r="BM2" s="258"/>
+      <c r="BN2" s="258"/>
+      <c r="BO2" s="258"/>
+      <c r="BP2" s="258"/>
+      <c r="BQ2" s="258"/>
+      <c r="BR2" s="258"/>
+      <c r="BS2" s="258"/>
+      <c r="BT2" s="258"/>
+      <c r="BU2" s="258"/>
+      <c r="BV2" s="258"/>
+      <c r="BW2" s="258"/>
+      <c r="BX2" s="258"/>
+      <c r="BY2" s="258"/>
+      <c r="BZ2" s="258"/>
+      <c r="CA2" s="258"/>
+      <c r="CB2" s="258"/>
+      <c r="CC2" s="258"/>
+      <c r="CD2" s="258"/>
+      <c r="CE2" s="258"/>
+      <c r="CF2" s="258"/>
+      <c r="CG2" s="258"/>
+      <c r="CH2" s="258"/>
+      <c r="CI2" s="258"/>
+      <c r="CJ2" s="258"/>
+      <c r="CK2" s="258"/>
+      <c r="CL2" s="258"/>
+      <c r="CM2" s="258"/>
+      <c r="CN2" s="258"/>
+      <c r="CO2" s="258"/>
+      <c r="CP2" s="258"/>
+      <c r="CQ2" s="258"/>
+      <c r="CR2" s="258"/>
+      <c r="CS2" s="258"/>
+      <c r="CT2" s="258"/>
+      <c r="CU2" s="258"/>
+      <c r="CV2" s="258"/>
+      <c r="CW2" s="258"/>
+      <c r="CX2" s="258"/>
+      <c r="CY2" s="258"/>
+      <c r="CZ2" s="258"/>
+      <c r="DA2" s="258"/>
+      <c r="DB2" s="258"/>
+      <c r="DC2" s="258"/>
+      <c r="DD2" s="258"/>
+      <c r="DE2" s="258"/>
+      <c r="DF2" s="258"/>
+      <c r="DG2" s="258"/>
+      <c r="DH2" s="258"/>
+      <c r="DI2" s="258"/>
+      <c r="DJ2" s="258"/>
+      <c r="DK2" s="258"/>
+      <c r="DL2" s="258"/>
+      <c r="DM2" s="258"/>
+      <c r="DN2" s="258"/>
+      <c r="DO2" s="258"/>
+      <c r="DP2" s="258"/>
+      <c r="DQ2" s="258"/>
+      <c r="DR2" s="258"/>
+      <c r="DS2" s="258"/>
+      <c r="DT2" s="258"/>
+      <c r="DU2" s="258"/>
+      <c r="DV2" s="258"/>
+      <c r="DW2" s="258"/>
+      <c r="DX2" s="258"/>
+      <c r="DY2" s="258"/>
+      <c r="DZ2" s="258"/>
+      <c r="EA2" s="258"/>
+      <c r="EB2" s="258"/>
+      <c r="EC2" s="258"/>
+      <c r="ED2" s="258"/>
+      <c r="EE2" s="258"/>
+      <c r="EF2" s="258"/>
+      <c r="EG2" s="258"/>
+      <c r="EH2" s="258"/>
+      <c r="EI2" s="258"/>
+      <c r="EJ2" s="258"/>
+      <c r="EK2" s="258"/>
+      <c r="EL2" s="258"/>
+      <c r="EM2" s="258"/>
+      <c r="EN2" s="258"/>
+      <c r="EO2" s="258"/>
+      <c r="EP2" s="258"/>
+      <c r="EQ2" s="258"/>
+      <c r="ER2" s="258"/>
+      <c r="ES2" s="258"/>
+      <c r="ET2" s="258"/>
+      <c r="EU2" s="258"/>
+      <c r="EV2" s="258"/>
+      <c r="EW2" s="258"/>
+      <c r="EX2" s="258"/>
+      <c r="EY2" s="258"/>
+      <c r="EZ2" s="258"/>
+      <c r="FA2" s="258"/>
       <c r="FJ2" s="21"/>
       <c r="FK2" s="21"/>
       <c r="FP2" s="1"/>
@@ -4761,21 +4811,21 @@
       <c r="D3" s="6"/>
       <c r="E3" s="20"/>
       <c r="F3" s="20"/>
-      <c r="G3" s="265"/>
-      <c r="H3" s="266"/>
-      <c r="I3" s="266"/>
-      <c r="J3" s="266"/>
-      <c r="K3" s="266"/>
-      <c r="L3" s="266"/>
-      <c r="M3" s="266"/>
-      <c r="N3" s="266"/>
-      <c r="O3" s="266"/>
-      <c r="P3" s="266"/>
-      <c r="Q3" s="266"/>
-      <c r="R3" s="266"/>
-      <c r="S3" s="266"/>
-      <c r="T3" s="266"/>
-      <c r="U3" s="267"/>
+      <c r="G3" s="262"/>
+      <c r="H3" s="263"/>
+      <c r="I3" s="263"/>
+      <c r="J3" s="263"/>
+      <c r="K3" s="263"/>
+      <c r="L3" s="263"/>
+      <c r="M3" s="263"/>
+      <c r="N3" s="263"/>
+      <c r="O3" s="263"/>
+      <c r="P3" s="263"/>
+      <c r="Q3" s="263"/>
+      <c r="R3" s="263"/>
+      <c r="S3" s="263"/>
+      <c r="T3" s="263"/>
+      <c r="U3" s="264"/>
       <c r="Y3" s="83" t="s">
         <v>10</v>
       </c>
@@ -4784,134 +4834,134 @@
         <v>179</v>
       </c>
       <c r="AB3" s="84"/>
-      <c r="AD3" s="252"/>
-      <c r="AE3" s="253"/>
-      <c r="AF3" s="254"/>
-      <c r="AG3" s="252"/>
-      <c r="AH3" s="253"/>
-      <c r="AI3" s="254"/>
-      <c r="AJ3" s="252"/>
-      <c r="AK3" s="253"/>
-      <c r="AL3" s="254"/>
-      <c r="AM3" s="261"/>
-      <c r="AN3" s="261"/>
-      <c r="AO3" s="261"/>
-      <c r="AP3" s="261"/>
-      <c r="AQ3" s="261"/>
-      <c r="AR3" s="261"/>
-      <c r="AS3" s="261"/>
-      <c r="AT3" s="261"/>
-      <c r="AU3" s="261"/>
-      <c r="AV3" s="261"/>
-      <c r="AW3" s="261"/>
-      <c r="AX3" s="261"/>
-      <c r="AY3" s="261"/>
-      <c r="AZ3" s="261"/>
-      <c r="BA3" s="261"/>
-      <c r="BB3" s="261"/>
-      <c r="BC3" s="261"/>
-      <c r="BD3" s="261"/>
-      <c r="BE3" s="261"/>
-      <c r="BF3" s="261"/>
-      <c r="BG3" s="261"/>
-      <c r="BH3" s="261"/>
-      <c r="BI3" s="261"/>
-      <c r="BJ3" s="261"/>
-      <c r="BK3" s="261"/>
-      <c r="BL3" s="261"/>
-      <c r="BM3" s="261"/>
-      <c r="BN3" s="261"/>
-      <c r="BO3" s="261"/>
-      <c r="BP3" s="261"/>
-      <c r="BQ3" s="261"/>
-      <c r="BR3" s="261"/>
-      <c r="BS3" s="261"/>
-      <c r="BT3" s="261"/>
-      <c r="BU3" s="261"/>
-      <c r="BV3" s="261"/>
-      <c r="BW3" s="261"/>
-      <c r="BX3" s="261"/>
-      <c r="BY3" s="261"/>
-      <c r="BZ3" s="261"/>
-      <c r="CA3" s="261"/>
-      <c r="CB3" s="261"/>
-      <c r="CC3" s="261"/>
-      <c r="CD3" s="261"/>
-      <c r="CE3" s="261"/>
-      <c r="CF3" s="261"/>
-      <c r="CG3" s="261"/>
-      <c r="CH3" s="261"/>
-      <c r="CI3" s="261"/>
-      <c r="CJ3" s="261"/>
-      <c r="CK3" s="261"/>
-      <c r="CL3" s="261"/>
-      <c r="CM3" s="261"/>
-      <c r="CN3" s="261"/>
-      <c r="CO3" s="261"/>
-      <c r="CP3" s="261"/>
-      <c r="CQ3" s="261"/>
-      <c r="CR3" s="261"/>
-      <c r="CS3" s="261"/>
-      <c r="CT3" s="261"/>
-      <c r="CU3" s="261"/>
-      <c r="CV3" s="261"/>
-      <c r="CW3" s="261"/>
-      <c r="CX3" s="261"/>
-      <c r="CY3" s="261"/>
-      <c r="CZ3" s="261"/>
-      <c r="DA3" s="261"/>
-      <c r="DB3" s="261"/>
-      <c r="DC3" s="261"/>
-      <c r="DD3" s="261"/>
-      <c r="DE3" s="261"/>
-      <c r="DF3" s="261"/>
-      <c r="DG3" s="261"/>
-      <c r="DH3" s="261"/>
-      <c r="DI3" s="261"/>
-      <c r="DJ3" s="261"/>
-      <c r="DK3" s="261"/>
-      <c r="DL3" s="261"/>
-      <c r="DM3" s="261"/>
-      <c r="DN3" s="261"/>
-      <c r="DO3" s="261"/>
-      <c r="DP3" s="261"/>
-      <c r="DQ3" s="261"/>
-      <c r="DR3" s="261"/>
-      <c r="DS3" s="261"/>
-      <c r="DT3" s="261"/>
-      <c r="DU3" s="261"/>
-      <c r="DV3" s="261"/>
-      <c r="DW3" s="261"/>
-      <c r="DX3" s="261"/>
-      <c r="DY3" s="261"/>
-      <c r="DZ3" s="261"/>
-      <c r="EA3" s="261"/>
-      <c r="EB3" s="261"/>
-      <c r="EC3" s="261"/>
-      <c r="ED3" s="261"/>
-      <c r="EE3" s="261"/>
-      <c r="EF3" s="261"/>
-      <c r="EG3" s="261"/>
-      <c r="EH3" s="261"/>
-      <c r="EI3" s="261"/>
-      <c r="EJ3" s="261"/>
-      <c r="EK3" s="261"/>
-      <c r="EL3" s="261"/>
-      <c r="EM3" s="261"/>
-      <c r="EN3" s="261"/>
-      <c r="EO3" s="261"/>
-      <c r="EP3" s="261"/>
-      <c r="EQ3" s="261"/>
-      <c r="ER3" s="261"/>
-      <c r="ES3" s="261"/>
-      <c r="ET3" s="261"/>
-      <c r="EU3" s="261"/>
-      <c r="EV3" s="261"/>
-      <c r="EW3" s="261"/>
-      <c r="EX3" s="261"/>
-      <c r="EY3" s="261"/>
-      <c r="EZ3" s="261"/>
-      <c r="FA3" s="261"/>
+      <c r="AD3" s="286"/>
+      <c r="AE3" s="287"/>
+      <c r="AF3" s="288"/>
+      <c r="AG3" s="171"/>
+      <c r="AH3" s="171"/>
+      <c r="AI3" s="171"/>
+      <c r="AJ3" s="171"/>
+      <c r="AK3" s="171"/>
+      <c r="AL3" s="171"/>
+      <c r="AM3" s="258"/>
+      <c r="AN3" s="258"/>
+      <c r="AO3" s="258"/>
+      <c r="AP3" s="258"/>
+      <c r="AQ3" s="258"/>
+      <c r="AR3" s="258"/>
+      <c r="AS3" s="258"/>
+      <c r="AT3" s="258"/>
+      <c r="AU3" s="258"/>
+      <c r="AV3" s="258"/>
+      <c r="AW3" s="258"/>
+      <c r="AX3" s="258"/>
+      <c r="AY3" s="258"/>
+      <c r="AZ3" s="258"/>
+      <c r="BA3" s="258"/>
+      <c r="BB3" s="258"/>
+      <c r="BC3" s="258"/>
+      <c r="BD3" s="258"/>
+      <c r="BE3" s="258"/>
+      <c r="BF3" s="258"/>
+      <c r="BG3" s="258"/>
+      <c r="BH3" s="258"/>
+      <c r="BI3" s="258"/>
+      <c r="BJ3" s="258"/>
+      <c r="BK3" s="258"/>
+      <c r="BL3" s="258"/>
+      <c r="BM3" s="258"/>
+      <c r="BN3" s="258"/>
+      <c r="BO3" s="258"/>
+      <c r="BP3" s="258"/>
+      <c r="BQ3" s="258"/>
+      <c r="BR3" s="258"/>
+      <c r="BS3" s="258"/>
+      <c r="BT3" s="258"/>
+      <c r="BU3" s="258"/>
+      <c r="BV3" s="258"/>
+      <c r="BW3" s="258"/>
+      <c r="BX3" s="258"/>
+      <c r="BY3" s="258"/>
+      <c r="BZ3" s="258"/>
+      <c r="CA3" s="258"/>
+      <c r="CB3" s="258"/>
+      <c r="CC3" s="258"/>
+      <c r="CD3" s="258"/>
+      <c r="CE3" s="258"/>
+      <c r="CF3" s="258"/>
+      <c r="CG3" s="258"/>
+      <c r="CH3" s="258"/>
+      <c r="CI3" s="258"/>
+      <c r="CJ3" s="258"/>
+      <c r="CK3" s="258"/>
+      <c r="CL3" s="258"/>
+      <c r="CM3" s="258"/>
+      <c r="CN3" s="258"/>
+      <c r="CO3" s="258"/>
+      <c r="CP3" s="258"/>
+      <c r="CQ3" s="258"/>
+      <c r="CR3" s="258"/>
+      <c r="CS3" s="258"/>
+      <c r="CT3" s="258"/>
+      <c r="CU3" s="258"/>
+      <c r="CV3" s="258"/>
+      <c r="CW3" s="258"/>
+      <c r="CX3" s="258"/>
+      <c r="CY3" s="258"/>
+      <c r="CZ3" s="258"/>
+      <c r="DA3" s="258"/>
+      <c r="DB3" s="258"/>
+      <c r="DC3" s="258"/>
+      <c r="DD3" s="258"/>
+      <c r="DE3" s="258"/>
+      <c r="DF3" s="258"/>
+      <c r="DG3" s="258"/>
+      <c r="DH3" s="258"/>
+      <c r="DI3" s="258"/>
+      <c r="DJ3" s="258"/>
+      <c r="DK3" s="258"/>
+      <c r="DL3" s="258"/>
+      <c r="DM3" s="258"/>
+      <c r="DN3" s="258"/>
+      <c r="DO3" s="258"/>
+      <c r="DP3" s="258"/>
+      <c r="DQ3" s="258"/>
+      <c r="DR3" s="258"/>
+      <c r="DS3" s="258"/>
+      <c r="DT3" s="258"/>
+      <c r="DU3" s="258"/>
+      <c r="DV3" s="258"/>
+      <c r="DW3" s="258"/>
+      <c r="DX3" s="258"/>
+      <c r="DY3" s="258"/>
+      <c r="DZ3" s="258"/>
+      <c r="EA3" s="258"/>
+      <c r="EB3" s="258"/>
+      <c r="EC3" s="258"/>
+      <c r="ED3" s="258"/>
+      <c r="EE3" s="258"/>
+      <c r="EF3" s="258"/>
+      <c r="EG3" s="258"/>
+      <c r="EH3" s="258"/>
+      <c r="EI3" s="258"/>
+      <c r="EJ3" s="258"/>
+      <c r="EK3" s="258"/>
+      <c r="EL3" s="258"/>
+      <c r="EM3" s="258"/>
+      <c r="EN3" s="258"/>
+      <c r="EO3" s="258"/>
+      <c r="EP3" s="258"/>
+      <c r="EQ3" s="258"/>
+      <c r="ER3" s="258"/>
+      <c r="ES3" s="258"/>
+      <c r="ET3" s="258"/>
+      <c r="EU3" s="258"/>
+      <c r="EV3" s="258"/>
+      <c r="EW3" s="258"/>
+      <c r="EX3" s="258"/>
+      <c r="EY3" s="258"/>
+      <c r="EZ3" s="258"/>
+      <c r="FA3" s="258"/>
       <c r="FJ3" s="22"/>
       <c r="FK3" s="22"/>
       <c r="FP3" s="1"/>
@@ -4926,21 +4976,21 @@
       <c r="D4" s="6"/>
       <c r="E4" s="20"/>
       <c r="F4" s="20"/>
-      <c r="G4" s="265"/>
-      <c r="H4" s="266"/>
-      <c r="I4" s="266"/>
-      <c r="J4" s="266"/>
-      <c r="K4" s="266"/>
-      <c r="L4" s="266"/>
-      <c r="M4" s="266"/>
-      <c r="N4" s="266"/>
-      <c r="O4" s="266"/>
-      <c r="P4" s="266"/>
-      <c r="Q4" s="266"/>
-      <c r="R4" s="266"/>
-      <c r="S4" s="266"/>
-      <c r="T4" s="266"/>
-      <c r="U4" s="267"/>
+      <c r="G4" s="262"/>
+      <c r="H4" s="263"/>
+      <c r="I4" s="263"/>
+      <c r="J4" s="263"/>
+      <c r="K4" s="263"/>
+      <c r="L4" s="263"/>
+      <c r="M4" s="263"/>
+      <c r="N4" s="263"/>
+      <c r="O4" s="263"/>
+      <c r="P4" s="263"/>
+      <c r="Q4" s="263"/>
+      <c r="R4" s="263"/>
+      <c r="S4" s="263"/>
+      <c r="T4" s="263"/>
+      <c r="U4" s="264"/>
       <c r="Y4" s="72" t="s">
         <v>52</v>
       </c>
@@ -4949,134 +4999,134 @@
         <v>180</v>
       </c>
       <c r="AB4" s="34"/>
-      <c r="AD4" s="252"/>
-      <c r="AE4" s="253"/>
-      <c r="AF4" s="254"/>
-      <c r="AG4" s="252"/>
-      <c r="AH4" s="253"/>
-      <c r="AI4" s="254"/>
-      <c r="AJ4" s="252"/>
-      <c r="AK4" s="253"/>
-      <c r="AL4" s="254"/>
-      <c r="AM4" s="261"/>
-      <c r="AN4" s="261"/>
-      <c r="AO4" s="261"/>
-      <c r="AP4" s="261"/>
-      <c r="AQ4" s="261"/>
-      <c r="AR4" s="261"/>
-      <c r="AS4" s="261"/>
-      <c r="AT4" s="261"/>
-      <c r="AU4" s="261"/>
-      <c r="AV4" s="261"/>
-      <c r="AW4" s="261"/>
-      <c r="AX4" s="261"/>
-      <c r="AY4" s="261"/>
-      <c r="AZ4" s="261"/>
-      <c r="BA4" s="261"/>
-      <c r="BB4" s="261"/>
-      <c r="BC4" s="261"/>
-      <c r="BD4" s="261"/>
-      <c r="BE4" s="261"/>
-      <c r="BF4" s="261"/>
-      <c r="BG4" s="261"/>
-      <c r="BH4" s="261"/>
-      <c r="BI4" s="261"/>
-      <c r="BJ4" s="261"/>
-      <c r="BK4" s="261"/>
-      <c r="BL4" s="261"/>
-      <c r="BM4" s="261"/>
-      <c r="BN4" s="261"/>
-      <c r="BO4" s="261"/>
-      <c r="BP4" s="261"/>
-      <c r="BQ4" s="261"/>
-      <c r="BR4" s="261"/>
-      <c r="BS4" s="261"/>
-      <c r="BT4" s="261"/>
-      <c r="BU4" s="261"/>
-      <c r="BV4" s="261"/>
-      <c r="BW4" s="261"/>
-      <c r="BX4" s="261"/>
-      <c r="BY4" s="261"/>
-      <c r="BZ4" s="261"/>
-      <c r="CA4" s="261"/>
-      <c r="CB4" s="261"/>
-      <c r="CC4" s="261"/>
-      <c r="CD4" s="261"/>
-      <c r="CE4" s="261"/>
-      <c r="CF4" s="261"/>
-      <c r="CG4" s="261"/>
-      <c r="CH4" s="261"/>
-      <c r="CI4" s="261"/>
-      <c r="CJ4" s="261"/>
-      <c r="CK4" s="261"/>
-      <c r="CL4" s="261"/>
-      <c r="CM4" s="261"/>
-      <c r="CN4" s="261"/>
-      <c r="CO4" s="261"/>
-      <c r="CP4" s="261"/>
-      <c r="CQ4" s="261"/>
-      <c r="CR4" s="261"/>
-      <c r="CS4" s="261"/>
-      <c r="CT4" s="261"/>
-      <c r="CU4" s="261"/>
-      <c r="CV4" s="261"/>
-      <c r="CW4" s="261"/>
-      <c r="CX4" s="261"/>
-      <c r="CY4" s="261"/>
-      <c r="CZ4" s="261"/>
-      <c r="DA4" s="261"/>
-      <c r="DB4" s="261"/>
-      <c r="DC4" s="261"/>
-      <c r="DD4" s="261"/>
-      <c r="DE4" s="261"/>
-      <c r="DF4" s="261"/>
-      <c r="DG4" s="261"/>
-      <c r="DH4" s="261"/>
-      <c r="DI4" s="261"/>
-      <c r="DJ4" s="261"/>
-      <c r="DK4" s="261"/>
-      <c r="DL4" s="261"/>
-      <c r="DM4" s="261"/>
-      <c r="DN4" s="261"/>
-      <c r="DO4" s="261"/>
-      <c r="DP4" s="261"/>
-      <c r="DQ4" s="261"/>
-      <c r="DR4" s="261"/>
-      <c r="DS4" s="261"/>
-      <c r="DT4" s="261"/>
-      <c r="DU4" s="261"/>
-      <c r="DV4" s="261"/>
-      <c r="DW4" s="261"/>
-      <c r="DX4" s="261"/>
-      <c r="DY4" s="261"/>
-      <c r="DZ4" s="261"/>
-      <c r="EA4" s="261"/>
-      <c r="EB4" s="261"/>
-      <c r="EC4" s="261"/>
-      <c r="ED4" s="261"/>
-      <c r="EE4" s="261"/>
-      <c r="EF4" s="261"/>
-      <c r="EG4" s="261"/>
-      <c r="EH4" s="261"/>
-      <c r="EI4" s="261"/>
-      <c r="EJ4" s="261"/>
-      <c r="EK4" s="261"/>
-      <c r="EL4" s="261"/>
-      <c r="EM4" s="261"/>
-      <c r="EN4" s="261"/>
-      <c r="EO4" s="261"/>
-      <c r="EP4" s="261"/>
-      <c r="EQ4" s="261"/>
-      <c r="ER4" s="261"/>
-      <c r="ES4" s="261"/>
-      <c r="ET4" s="261"/>
-      <c r="EU4" s="261"/>
-      <c r="EV4" s="261"/>
-      <c r="EW4" s="261"/>
-      <c r="EX4" s="261"/>
-      <c r="EY4" s="261"/>
-      <c r="EZ4" s="261"/>
-      <c r="FA4" s="261"/>
+      <c r="AD4" s="289"/>
+      <c r="AE4" s="290"/>
+      <c r="AF4" s="291"/>
+      <c r="AG4" s="171"/>
+      <c r="AH4" s="171"/>
+      <c r="AI4" s="171"/>
+      <c r="AJ4" s="171"/>
+      <c r="AK4" s="171"/>
+      <c r="AL4" s="171"/>
+      <c r="AM4" s="258"/>
+      <c r="AN4" s="258"/>
+      <c r="AO4" s="258"/>
+      <c r="AP4" s="258"/>
+      <c r="AQ4" s="258"/>
+      <c r="AR4" s="258"/>
+      <c r="AS4" s="258"/>
+      <c r="AT4" s="258"/>
+      <c r="AU4" s="258"/>
+      <c r="AV4" s="258"/>
+      <c r="AW4" s="258"/>
+      <c r="AX4" s="258"/>
+      <c r="AY4" s="258"/>
+      <c r="AZ4" s="258"/>
+      <c r="BA4" s="258"/>
+      <c r="BB4" s="258"/>
+      <c r="BC4" s="258"/>
+      <c r="BD4" s="258"/>
+      <c r="BE4" s="258"/>
+      <c r="BF4" s="258"/>
+      <c r="BG4" s="258"/>
+      <c r="BH4" s="258"/>
+      <c r="BI4" s="258"/>
+      <c r="BJ4" s="258"/>
+      <c r="BK4" s="258"/>
+      <c r="BL4" s="258"/>
+      <c r="BM4" s="258"/>
+      <c r="BN4" s="258"/>
+      <c r="BO4" s="258"/>
+      <c r="BP4" s="258"/>
+      <c r="BQ4" s="258"/>
+      <c r="BR4" s="258"/>
+      <c r="BS4" s="258"/>
+      <c r="BT4" s="258"/>
+      <c r="BU4" s="258"/>
+      <c r="BV4" s="258"/>
+      <c r="BW4" s="258"/>
+      <c r="BX4" s="258"/>
+      <c r="BY4" s="258"/>
+      <c r="BZ4" s="258"/>
+      <c r="CA4" s="258"/>
+      <c r="CB4" s="258"/>
+      <c r="CC4" s="258"/>
+      <c r="CD4" s="258"/>
+      <c r="CE4" s="258"/>
+      <c r="CF4" s="258"/>
+      <c r="CG4" s="258"/>
+      <c r="CH4" s="258"/>
+      <c r="CI4" s="258"/>
+      <c r="CJ4" s="258"/>
+      <c r="CK4" s="258"/>
+      <c r="CL4" s="258"/>
+      <c r="CM4" s="258"/>
+      <c r="CN4" s="258"/>
+      <c r="CO4" s="258"/>
+      <c r="CP4" s="258"/>
+      <c r="CQ4" s="258"/>
+      <c r="CR4" s="258"/>
+      <c r="CS4" s="258"/>
+      <c r="CT4" s="258"/>
+      <c r="CU4" s="258"/>
+      <c r="CV4" s="258"/>
+      <c r="CW4" s="258"/>
+      <c r="CX4" s="258"/>
+      <c r="CY4" s="258"/>
+      <c r="CZ4" s="258"/>
+      <c r="DA4" s="258"/>
+      <c r="DB4" s="258"/>
+      <c r="DC4" s="258"/>
+      <c r="DD4" s="258"/>
+      <c r="DE4" s="258"/>
+      <c r="DF4" s="258"/>
+      <c r="DG4" s="258"/>
+      <c r="DH4" s="258"/>
+      <c r="DI4" s="258"/>
+      <c r="DJ4" s="258"/>
+      <c r="DK4" s="258"/>
+      <c r="DL4" s="258"/>
+      <c r="DM4" s="258"/>
+      <c r="DN4" s="258"/>
+      <c r="DO4" s="258"/>
+      <c r="DP4" s="258"/>
+      <c r="DQ4" s="258"/>
+      <c r="DR4" s="258"/>
+      <c r="DS4" s="258"/>
+      <c r="DT4" s="258"/>
+      <c r="DU4" s="258"/>
+      <c r="DV4" s="258"/>
+      <c r="DW4" s="258"/>
+      <c r="DX4" s="258"/>
+      <c r="DY4" s="258"/>
+      <c r="DZ4" s="258"/>
+      <c r="EA4" s="258"/>
+      <c r="EB4" s="258"/>
+      <c r="EC4" s="258"/>
+      <c r="ED4" s="258"/>
+      <c r="EE4" s="258"/>
+      <c r="EF4" s="258"/>
+      <c r="EG4" s="258"/>
+      <c r="EH4" s="258"/>
+      <c r="EI4" s="258"/>
+      <c r="EJ4" s="258"/>
+      <c r="EK4" s="258"/>
+      <c r="EL4" s="258"/>
+      <c r="EM4" s="258"/>
+      <c r="EN4" s="258"/>
+      <c r="EO4" s="258"/>
+      <c r="EP4" s="258"/>
+      <c r="EQ4" s="258"/>
+      <c r="ER4" s="258"/>
+      <c r="ES4" s="258"/>
+      <c r="ET4" s="258"/>
+      <c r="EU4" s="258"/>
+      <c r="EV4" s="258"/>
+      <c r="EW4" s="258"/>
+      <c r="EX4" s="258"/>
+      <c r="EY4" s="258"/>
+      <c r="EZ4" s="258"/>
+      <c r="FA4" s="258"/>
       <c r="FJ4" s="22"/>
       <c r="FK4" s="22"/>
       <c r="FP4" s="1"/>
@@ -5091,21 +5141,21 @@
       <c r="D5" s="6"/>
       <c r="E5" s="20"/>
       <c r="F5" s="20"/>
-      <c r="G5" s="265"/>
-      <c r="H5" s="266"/>
-      <c r="I5" s="266"/>
-      <c r="J5" s="266"/>
-      <c r="K5" s="266"/>
-      <c r="L5" s="266"/>
-      <c r="M5" s="266"/>
-      <c r="N5" s="266"/>
-      <c r="O5" s="266"/>
-      <c r="P5" s="266"/>
-      <c r="Q5" s="266"/>
-      <c r="R5" s="266"/>
-      <c r="S5" s="266"/>
-      <c r="T5" s="266"/>
-      <c r="U5" s="267"/>
+      <c r="G5" s="262"/>
+      <c r="H5" s="263"/>
+      <c r="I5" s="263"/>
+      <c r="J5" s="263"/>
+      <c r="K5" s="263"/>
+      <c r="L5" s="263"/>
+      <c r="M5" s="263"/>
+      <c r="N5" s="263"/>
+      <c r="O5" s="263"/>
+      <c r="P5" s="263"/>
+      <c r="Q5" s="263"/>
+      <c r="R5" s="263"/>
+      <c r="S5" s="263"/>
+      <c r="T5" s="263"/>
+      <c r="U5" s="264"/>
       <c r="Y5" s="72" t="s">
         <v>53</v>
       </c>
@@ -5114,134 +5164,134 @@
         <v>181</v>
       </c>
       <c r="AB5" s="34"/>
-      <c r="AD5" s="252"/>
-      <c r="AE5" s="253"/>
-      <c r="AF5" s="254"/>
-      <c r="AG5" s="252"/>
-      <c r="AH5" s="253"/>
-      <c r="AI5" s="254"/>
-      <c r="AJ5" s="252"/>
-      <c r="AK5" s="253"/>
-      <c r="AL5" s="254"/>
-      <c r="AM5" s="261"/>
-      <c r="AN5" s="261"/>
-      <c r="AO5" s="261"/>
-      <c r="AP5" s="261"/>
-      <c r="AQ5" s="261"/>
-      <c r="AR5" s="261"/>
-      <c r="AS5" s="261"/>
-      <c r="AT5" s="261"/>
-      <c r="AU5" s="261"/>
-      <c r="AV5" s="261"/>
-      <c r="AW5" s="261"/>
-      <c r="AX5" s="261"/>
-      <c r="AY5" s="261"/>
-      <c r="AZ5" s="261"/>
-      <c r="BA5" s="261"/>
-      <c r="BB5" s="261"/>
-      <c r="BC5" s="261"/>
-      <c r="BD5" s="261"/>
-      <c r="BE5" s="261"/>
-      <c r="BF5" s="261"/>
-      <c r="BG5" s="261"/>
-      <c r="BH5" s="261"/>
-      <c r="BI5" s="261"/>
-      <c r="BJ5" s="261"/>
-      <c r="BK5" s="261"/>
-      <c r="BL5" s="261"/>
-      <c r="BM5" s="261"/>
-      <c r="BN5" s="261"/>
-      <c r="BO5" s="261"/>
-      <c r="BP5" s="261"/>
-      <c r="BQ5" s="261"/>
-      <c r="BR5" s="261"/>
-      <c r="BS5" s="261"/>
-      <c r="BT5" s="261"/>
-      <c r="BU5" s="261"/>
-      <c r="BV5" s="261"/>
-      <c r="BW5" s="261"/>
-      <c r="BX5" s="261"/>
-      <c r="BY5" s="261"/>
-      <c r="BZ5" s="261"/>
-      <c r="CA5" s="261"/>
-      <c r="CB5" s="261"/>
-      <c r="CC5" s="261"/>
-      <c r="CD5" s="261"/>
-      <c r="CE5" s="261"/>
-      <c r="CF5" s="261"/>
-      <c r="CG5" s="261"/>
-      <c r="CH5" s="261"/>
-      <c r="CI5" s="261"/>
-      <c r="CJ5" s="261"/>
-      <c r="CK5" s="261"/>
-      <c r="CL5" s="261"/>
-      <c r="CM5" s="261"/>
-      <c r="CN5" s="261"/>
-      <c r="CO5" s="261"/>
-      <c r="CP5" s="261"/>
-      <c r="CQ5" s="261"/>
-      <c r="CR5" s="261"/>
-      <c r="CS5" s="261"/>
-      <c r="CT5" s="261"/>
-      <c r="CU5" s="261"/>
-      <c r="CV5" s="261"/>
-      <c r="CW5" s="261"/>
-      <c r="CX5" s="261"/>
-      <c r="CY5" s="261"/>
-      <c r="CZ5" s="261"/>
-      <c r="DA5" s="261"/>
-      <c r="DB5" s="261"/>
-      <c r="DC5" s="261"/>
-      <c r="DD5" s="261"/>
-      <c r="DE5" s="261"/>
-      <c r="DF5" s="261"/>
-      <c r="DG5" s="261"/>
-      <c r="DH5" s="261"/>
-      <c r="DI5" s="261"/>
-      <c r="DJ5" s="261"/>
-      <c r="DK5" s="261"/>
-      <c r="DL5" s="261"/>
-      <c r="DM5" s="261"/>
-      <c r="DN5" s="261"/>
-      <c r="DO5" s="261"/>
-      <c r="DP5" s="261"/>
-      <c r="DQ5" s="261"/>
-      <c r="DR5" s="261"/>
-      <c r="DS5" s="261"/>
-      <c r="DT5" s="261"/>
-      <c r="DU5" s="261"/>
-      <c r="DV5" s="261"/>
-      <c r="DW5" s="261"/>
-      <c r="DX5" s="261"/>
-      <c r="DY5" s="261"/>
-      <c r="DZ5" s="261"/>
-      <c r="EA5" s="261"/>
-      <c r="EB5" s="261"/>
-      <c r="EC5" s="261"/>
-      <c r="ED5" s="261"/>
-      <c r="EE5" s="261"/>
-      <c r="EF5" s="261"/>
-      <c r="EG5" s="261"/>
-      <c r="EH5" s="261"/>
-      <c r="EI5" s="261"/>
-      <c r="EJ5" s="261"/>
-      <c r="EK5" s="261"/>
-      <c r="EL5" s="261"/>
-      <c r="EM5" s="261"/>
-      <c r="EN5" s="261"/>
-      <c r="EO5" s="261"/>
-      <c r="EP5" s="261"/>
-      <c r="EQ5" s="261"/>
-      <c r="ER5" s="261"/>
-      <c r="ES5" s="261"/>
-      <c r="ET5" s="261"/>
-      <c r="EU5" s="261"/>
-      <c r="EV5" s="261"/>
-      <c r="EW5" s="261"/>
-      <c r="EX5" s="261"/>
-      <c r="EY5" s="261"/>
-      <c r="EZ5" s="261"/>
-      <c r="FA5" s="261"/>
+      <c r="AD5" s="289"/>
+      <c r="AE5" s="290"/>
+      <c r="AF5" s="291"/>
+      <c r="AG5" s="171"/>
+      <c r="AH5" s="171"/>
+      <c r="AI5" s="171"/>
+      <c r="AJ5" s="171"/>
+      <c r="AK5" s="171"/>
+      <c r="AL5" s="171"/>
+      <c r="AM5" s="258"/>
+      <c r="AN5" s="258"/>
+      <c r="AO5" s="258"/>
+      <c r="AP5" s="258"/>
+      <c r="AQ5" s="258"/>
+      <c r="AR5" s="258"/>
+      <c r="AS5" s="258"/>
+      <c r="AT5" s="258"/>
+      <c r="AU5" s="258"/>
+      <c r="AV5" s="258"/>
+      <c r="AW5" s="258"/>
+      <c r="AX5" s="258"/>
+      <c r="AY5" s="258"/>
+      <c r="AZ5" s="258"/>
+      <c r="BA5" s="258"/>
+      <c r="BB5" s="258"/>
+      <c r="BC5" s="258"/>
+      <c r="BD5" s="258"/>
+      <c r="BE5" s="258"/>
+      <c r="BF5" s="258"/>
+      <c r="BG5" s="258"/>
+      <c r="BH5" s="258"/>
+      <c r="BI5" s="258"/>
+      <c r="BJ5" s="258"/>
+      <c r="BK5" s="258"/>
+      <c r="BL5" s="258"/>
+      <c r="BM5" s="258"/>
+      <c r="BN5" s="258"/>
+      <c r="BO5" s="258"/>
+      <c r="BP5" s="258"/>
+      <c r="BQ5" s="258"/>
+      <c r="BR5" s="258"/>
+      <c r="BS5" s="258"/>
+      <c r="BT5" s="258"/>
+      <c r="BU5" s="258"/>
+      <c r="BV5" s="258"/>
+      <c r="BW5" s="258"/>
+      <c r="BX5" s="258"/>
+      <c r="BY5" s="258"/>
+      <c r="BZ5" s="258"/>
+      <c r="CA5" s="258"/>
+      <c r="CB5" s="258"/>
+      <c r="CC5" s="258"/>
+      <c r="CD5" s="258"/>
+      <c r="CE5" s="258"/>
+      <c r="CF5" s="258"/>
+      <c r="CG5" s="258"/>
+      <c r="CH5" s="258"/>
+      <c r="CI5" s="258"/>
+      <c r="CJ5" s="258"/>
+      <c r="CK5" s="258"/>
+      <c r="CL5" s="258"/>
+      <c r="CM5" s="258"/>
+      <c r="CN5" s="258"/>
+      <c r="CO5" s="258"/>
+      <c r="CP5" s="258"/>
+      <c r="CQ5" s="258"/>
+      <c r="CR5" s="258"/>
+      <c r="CS5" s="258"/>
+      <c r="CT5" s="258"/>
+      <c r="CU5" s="258"/>
+      <c r="CV5" s="258"/>
+      <c r="CW5" s="258"/>
+      <c r="CX5" s="258"/>
+      <c r="CY5" s="258"/>
+      <c r="CZ5" s="258"/>
+      <c r="DA5" s="258"/>
+      <c r="DB5" s="258"/>
+      <c r="DC5" s="258"/>
+      <c r="DD5" s="258"/>
+      <c r="DE5" s="258"/>
+      <c r="DF5" s="258"/>
+      <c r="DG5" s="258"/>
+      <c r="DH5" s="258"/>
+      <c r="DI5" s="258"/>
+      <c r="DJ5" s="258"/>
+      <c r="DK5" s="258"/>
+      <c r="DL5" s="258"/>
+      <c r="DM5" s="258"/>
+      <c r="DN5" s="258"/>
+      <c r="DO5" s="258"/>
+      <c r="DP5" s="258"/>
+      <c r="DQ5" s="258"/>
+      <c r="DR5" s="258"/>
+      <c r="DS5" s="258"/>
+      <c r="DT5" s="258"/>
+      <c r="DU5" s="258"/>
+      <c r="DV5" s="258"/>
+      <c r="DW5" s="258"/>
+      <c r="DX5" s="258"/>
+      <c r="DY5" s="258"/>
+      <c r="DZ5" s="258"/>
+      <c r="EA5" s="258"/>
+      <c r="EB5" s="258"/>
+      <c r="EC5" s="258"/>
+      <c r="ED5" s="258"/>
+      <c r="EE5" s="258"/>
+      <c r="EF5" s="258"/>
+      <c r="EG5" s="258"/>
+      <c r="EH5" s="258"/>
+      <c r="EI5" s="258"/>
+      <c r="EJ5" s="258"/>
+      <c r="EK5" s="258"/>
+      <c r="EL5" s="258"/>
+      <c r="EM5" s="258"/>
+      <c r="EN5" s="258"/>
+      <c r="EO5" s="258"/>
+      <c r="EP5" s="258"/>
+      <c r="EQ5" s="258"/>
+      <c r="ER5" s="258"/>
+      <c r="ES5" s="258"/>
+      <c r="ET5" s="258"/>
+      <c r="EU5" s="258"/>
+      <c r="EV5" s="258"/>
+      <c r="EW5" s="258"/>
+      <c r="EX5" s="258"/>
+      <c r="EY5" s="258"/>
+      <c r="EZ5" s="258"/>
+      <c r="FA5" s="258"/>
       <c r="FJ5" s="22"/>
       <c r="FK5" s="22"/>
       <c r="FP5" s="1"/>
@@ -5256,21 +5306,21 @@
       <c r="D6" s="6"/>
       <c r="E6" s="20"/>
       <c r="F6" s="20"/>
-      <c r="G6" s="265"/>
-      <c r="H6" s="266"/>
-      <c r="I6" s="266"/>
-      <c r="J6" s="266"/>
-      <c r="K6" s="266"/>
-      <c r="L6" s="266"/>
-      <c r="M6" s="266"/>
-      <c r="N6" s="266"/>
-      <c r="O6" s="266"/>
-      <c r="P6" s="266"/>
-      <c r="Q6" s="266"/>
-      <c r="R6" s="266"/>
-      <c r="S6" s="266"/>
-      <c r="T6" s="266"/>
-      <c r="U6" s="267"/>
+      <c r="G6" s="262"/>
+      <c r="H6" s="263"/>
+      <c r="I6" s="263"/>
+      <c r="J6" s="263"/>
+      <c r="K6" s="263"/>
+      <c r="L6" s="263"/>
+      <c r="M6" s="263"/>
+      <c r="N6" s="263"/>
+      <c r="O6" s="263"/>
+      <c r="P6" s="263"/>
+      <c r="Q6" s="263"/>
+      <c r="R6" s="263"/>
+      <c r="S6" s="263"/>
+      <c r="T6" s="263"/>
+      <c r="U6" s="264"/>
       <c r="Y6" s="72" t="s">
         <v>54</v>
       </c>
@@ -5279,134 +5329,134 @@
         <v>182</v>
       </c>
       <c r="AB6" s="34"/>
-      <c r="AD6" s="252"/>
-      <c r="AE6" s="253"/>
-      <c r="AF6" s="254"/>
-      <c r="AG6" s="252"/>
-      <c r="AH6" s="253"/>
-      <c r="AI6" s="254"/>
-      <c r="AJ6" s="252"/>
-      <c r="AK6" s="253"/>
-      <c r="AL6" s="254"/>
-      <c r="AM6" s="261"/>
-      <c r="AN6" s="261"/>
-      <c r="AO6" s="261"/>
-      <c r="AP6" s="261"/>
-      <c r="AQ6" s="261"/>
-      <c r="AR6" s="261"/>
-      <c r="AS6" s="261"/>
-      <c r="AT6" s="261"/>
-      <c r="AU6" s="261"/>
-      <c r="AV6" s="261"/>
-      <c r="AW6" s="261"/>
-      <c r="AX6" s="261"/>
-      <c r="AY6" s="261"/>
-      <c r="AZ6" s="261"/>
-      <c r="BA6" s="261"/>
-      <c r="BB6" s="261"/>
-      <c r="BC6" s="261"/>
-      <c r="BD6" s="261"/>
-      <c r="BE6" s="261"/>
-      <c r="BF6" s="261"/>
-      <c r="BG6" s="261"/>
-      <c r="BH6" s="261"/>
-      <c r="BI6" s="261"/>
-      <c r="BJ6" s="261"/>
-      <c r="BK6" s="261"/>
-      <c r="BL6" s="261"/>
-      <c r="BM6" s="261"/>
-      <c r="BN6" s="261"/>
-      <c r="BO6" s="261"/>
-      <c r="BP6" s="261"/>
-      <c r="BQ6" s="261"/>
-      <c r="BR6" s="261"/>
-      <c r="BS6" s="261"/>
-      <c r="BT6" s="261"/>
-      <c r="BU6" s="261"/>
-      <c r="BV6" s="261"/>
-      <c r="BW6" s="261"/>
-      <c r="BX6" s="261"/>
-      <c r="BY6" s="261"/>
-      <c r="BZ6" s="261"/>
-      <c r="CA6" s="261"/>
-      <c r="CB6" s="261"/>
-      <c r="CC6" s="261"/>
-      <c r="CD6" s="261"/>
-      <c r="CE6" s="261"/>
-      <c r="CF6" s="261"/>
-      <c r="CG6" s="261"/>
-      <c r="CH6" s="261"/>
-      <c r="CI6" s="261"/>
-      <c r="CJ6" s="261"/>
-      <c r="CK6" s="261"/>
-      <c r="CL6" s="261"/>
-      <c r="CM6" s="261"/>
-      <c r="CN6" s="261"/>
-      <c r="CO6" s="261"/>
-      <c r="CP6" s="261"/>
-      <c r="CQ6" s="261"/>
-      <c r="CR6" s="261"/>
-      <c r="CS6" s="261"/>
-      <c r="CT6" s="261"/>
-      <c r="CU6" s="261"/>
-      <c r="CV6" s="261"/>
-      <c r="CW6" s="261"/>
-      <c r="CX6" s="261"/>
-      <c r="CY6" s="261"/>
-      <c r="CZ6" s="261"/>
-      <c r="DA6" s="261"/>
-      <c r="DB6" s="261"/>
-      <c r="DC6" s="261"/>
-      <c r="DD6" s="261"/>
-      <c r="DE6" s="261"/>
-      <c r="DF6" s="261"/>
-      <c r="DG6" s="261"/>
-      <c r="DH6" s="261"/>
-      <c r="DI6" s="261"/>
-      <c r="DJ6" s="261"/>
-      <c r="DK6" s="261"/>
-      <c r="DL6" s="261"/>
-      <c r="DM6" s="261"/>
-      <c r="DN6" s="261"/>
-      <c r="DO6" s="261"/>
-      <c r="DP6" s="261"/>
-      <c r="DQ6" s="261"/>
-      <c r="DR6" s="261"/>
-      <c r="DS6" s="261"/>
-      <c r="DT6" s="261"/>
-      <c r="DU6" s="261"/>
-      <c r="DV6" s="261"/>
-      <c r="DW6" s="261"/>
-      <c r="DX6" s="261"/>
-      <c r="DY6" s="261"/>
-      <c r="DZ6" s="261"/>
-      <c r="EA6" s="261"/>
-      <c r="EB6" s="261"/>
-      <c r="EC6" s="261"/>
-      <c r="ED6" s="261"/>
-      <c r="EE6" s="261"/>
-      <c r="EF6" s="261"/>
-      <c r="EG6" s="261"/>
-      <c r="EH6" s="261"/>
-      <c r="EI6" s="261"/>
-      <c r="EJ6" s="261"/>
-      <c r="EK6" s="261"/>
-      <c r="EL6" s="261"/>
-      <c r="EM6" s="261"/>
-      <c r="EN6" s="261"/>
-      <c r="EO6" s="261"/>
-      <c r="EP6" s="261"/>
-      <c r="EQ6" s="261"/>
-      <c r="ER6" s="261"/>
-      <c r="ES6" s="261"/>
-      <c r="ET6" s="261"/>
-      <c r="EU6" s="261"/>
-      <c r="EV6" s="261"/>
-      <c r="EW6" s="261"/>
-      <c r="EX6" s="261"/>
-      <c r="EY6" s="261"/>
-      <c r="EZ6" s="261"/>
-      <c r="FA6" s="261"/>
+      <c r="AD6" s="289"/>
+      <c r="AE6" s="290"/>
+      <c r="AF6" s="291"/>
+      <c r="AG6" s="171"/>
+      <c r="AH6" s="171"/>
+      <c r="AI6" s="171"/>
+      <c r="AJ6" s="171"/>
+      <c r="AK6" s="171"/>
+      <c r="AL6" s="171"/>
+      <c r="AM6" s="258"/>
+      <c r="AN6" s="258"/>
+      <c r="AO6" s="258"/>
+      <c r="AP6" s="258"/>
+      <c r="AQ6" s="258"/>
+      <c r="AR6" s="258"/>
+      <c r="AS6" s="258"/>
+      <c r="AT6" s="258"/>
+      <c r="AU6" s="258"/>
+      <c r="AV6" s="258"/>
+      <c r="AW6" s="258"/>
+      <c r="AX6" s="258"/>
+      <c r="AY6" s="258"/>
+      <c r="AZ6" s="258"/>
+      <c r="BA6" s="258"/>
+      <c r="BB6" s="258"/>
+      <c r="BC6" s="258"/>
+      <c r="BD6" s="258"/>
+      <c r="BE6" s="258"/>
+      <c r="BF6" s="258"/>
+      <c r="BG6" s="258"/>
+      <c r="BH6" s="258"/>
+      <c r="BI6" s="258"/>
+      <c r="BJ6" s="258"/>
+      <c r="BK6" s="258"/>
+      <c r="BL6" s="258"/>
+      <c r="BM6" s="258"/>
+      <c r="BN6" s="258"/>
+      <c r="BO6" s="258"/>
+      <c r="BP6" s="258"/>
+      <c r="BQ6" s="258"/>
+      <c r="BR6" s="258"/>
+      <c r="BS6" s="258"/>
+      <c r="BT6" s="258"/>
+      <c r="BU6" s="258"/>
+      <c r="BV6" s="258"/>
+      <c r="BW6" s="258"/>
+      <c r="BX6" s="258"/>
+      <c r="BY6" s="258"/>
+      <c r="BZ6" s="258"/>
+      <c r="CA6" s="258"/>
+      <c r="CB6" s="258"/>
+      <c r="CC6" s="258"/>
+      <c r="CD6" s="258"/>
+      <c r="CE6" s="258"/>
+      <c r="CF6" s="258"/>
+      <c r="CG6" s="258"/>
+      <c r="CH6" s="258"/>
+      <c r="CI6" s="258"/>
+      <c r="CJ6" s="258"/>
+      <c r="CK6" s="258"/>
+      <c r="CL6" s="258"/>
+      <c r="CM6" s="258"/>
+      <c r="CN6" s="258"/>
+      <c r="CO6" s="258"/>
+      <c r="CP6" s="258"/>
+      <c r="CQ6" s="258"/>
+      <c r="CR6" s="258"/>
+      <c r="CS6" s="258"/>
+      <c r="CT6" s="258"/>
+      <c r="CU6" s="258"/>
+      <c r="CV6" s="258"/>
+      <c r="CW6" s="258"/>
+      <c r="CX6" s="258"/>
+      <c r="CY6" s="258"/>
+      <c r="CZ6" s="258"/>
+      <c r="DA6" s="258"/>
+      <c r="DB6" s="258"/>
+      <c r="DC6" s="258"/>
+      <c r="DD6" s="258"/>
+      <c r="DE6" s="258"/>
+      <c r="DF6" s="258"/>
+      <c r="DG6" s="258"/>
+      <c r="DH6" s="258"/>
+      <c r="DI6" s="258"/>
+      <c r="DJ6" s="258"/>
+      <c r="DK6" s="258"/>
+      <c r="DL6" s="258"/>
+      <c r="DM6" s="258"/>
+      <c r="DN6" s="258"/>
+      <c r="DO6" s="258"/>
+      <c r="DP6" s="258"/>
+      <c r="DQ6" s="258"/>
+      <c r="DR6" s="258"/>
+      <c r="DS6" s="258"/>
+      <c r="DT6" s="258"/>
+      <c r="DU6" s="258"/>
+      <c r="DV6" s="258"/>
+      <c r="DW6" s="258"/>
+      <c r="DX6" s="258"/>
+      <c r="DY6" s="258"/>
+      <c r="DZ6" s="258"/>
+      <c r="EA6" s="258"/>
+      <c r="EB6" s="258"/>
+      <c r="EC6" s="258"/>
+      <c r="ED6" s="258"/>
+      <c r="EE6" s="258"/>
+      <c r="EF6" s="258"/>
+      <c r="EG6" s="258"/>
+      <c r="EH6" s="258"/>
+      <c r="EI6" s="258"/>
+      <c r="EJ6" s="258"/>
+      <c r="EK6" s="258"/>
+      <c r="EL6" s="258"/>
+      <c r="EM6" s="258"/>
+      <c r="EN6" s="258"/>
+      <c r="EO6" s="258"/>
+      <c r="EP6" s="258"/>
+      <c r="EQ6" s="258"/>
+      <c r="ER6" s="258"/>
+      <c r="ES6" s="258"/>
+      <c r="ET6" s="258"/>
+      <c r="EU6" s="258"/>
+      <c r="EV6" s="258"/>
+      <c r="EW6" s="258"/>
+      <c r="EX6" s="258"/>
+      <c r="EY6" s="258"/>
+      <c r="EZ6" s="258"/>
+      <c r="FA6" s="258"/>
       <c r="FJ6" s="22"/>
       <c r="FK6" s="22"/>
       <c r="FP6" s="1"/>
@@ -5421,21 +5471,21 @@
       <c r="D7" s="6"/>
       <c r="E7" s="20"/>
       <c r="F7" s="20"/>
-      <c r="G7" s="268"/>
-      <c r="H7" s="269"/>
-      <c r="I7" s="269"/>
-      <c r="J7" s="269"/>
-      <c r="K7" s="269"/>
-      <c r="L7" s="269"/>
-      <c r="M7" s="269"/>
-      <c r="N7" s="269"/>
-      <c r="O7" s="269"/>
-      <c r="P7" s="269"/>
-      <c r="Q7" s="269"/>
-      <c r="R7" s="269"/>
-      <c r="S7" s="269"/>
-      <c r="T7" s="269"/>
-      <c r="U7" s="270"/>
+      <c r="G7" s="265"/>
+      <c r="H7" s="266"/>
+      <c r="I7" s="266"/>
+      <c r="J7" s="266"/>
+      <c r="K7" s="266"/>
+      <c r="L7" s="266"/>
+      <c r="M7" s="266"/>
+      <c r="N7" s="266"/>
+      <c r="O7" s="266"/>
+      <c r="P7" s="266"/>
+      <c r="Q7" s="266"/>
+      <c r="R7" s="266"/>
+      <c r="S7" s="266"/>
+      <c r="T7" s="266"/>
+      <c r="U7" s="267"/>
       <c r="Y7" s="76" t="s">
         <v>55</v>
       </c>
@@ -5444,134 +5494,134 @@
         <v>183</v>
       </c>
       <c r="AB7" s="48"/>
-      <c r="AD7" s="255"/>
-      <c r="AE7" s="256"/>
-      <c r="AF7" s="257"/>
-      <c r="AG7" s="255"/>
-      <c r="AH7" s="256"/>
-      <c r="AI7" s="257"/>
-      <c r="AJ7" s="255"/>
-      <c r="AK7" s="256"/>
-      <c r="AL7" s="257"/>
-      <c r="AM7" s="261"/>
-      <c r="AN7" s="261"/>
-      <c r="AO7" s="261"/>
-      <c r="AP7" s="261"/>
-      <c r="AQ7" s="261"/>
-      <c r="AR7" s="261"/>
-      <c r="AS7" s="261"/>
-      <c r="AT7" s="261"/>
-      <c r="AU7" s="261"/>
-      <c r="AV7" s="261"/>
-      <c r="AW7" s="261"/>
-      <c r="AX7" s="261"/>
-      <c r="AY7" s="261"/>
-      <c r="AZ7" s="261"/>
-      <c r="BA7" s="261"/>
-      <c r="BB7" s="261"/>
-      <c r="BC7" s="261"/>
-      <c r="BD7" s="261"/>
-      <c r="BE7" s="261"/>
-      <c r="BF7" s="261"/>
-      <c r="BG7" s="261"/>
-      <c r="BH7" s="261"/>
-      <c r="BI7" s="261"/>
-      <c r="BJ7" s="261"/>
-      <c r="BK7" s="261"/>
-      <c r="BL7" s="261"/>
-      <c r="BM7" s="261"/>
-      <c r="BN7" s="261"/>
-      <c r="BO7" s="261"/>
-      <c r="BP7" s="261"/>
-      <c r="BQ7" s="261"/>
-      <c r="BR7" s="261"/>
-      <c r="BS7" s="261"/>
-      <c r="BT7" s="261"/>
-      <c r="BU7" s="261"/>
-      <c r="BV7" s="261"/>
-      <c r="BW7" s="261"/>
-      <c r="BX7" s="261"/>
-      <c r="BY7" s="261"/>
-      <c r="BZ7" s="261"/>
-      <c r="CA7" s="261"/>
-      <c r="CB7" s="261"/>
-      <c r="CC7" s="261"/>
-      <c r="CD7" s="261"/>
-      <c r="CE7" s="261"/>
-      <c r="CF7" s="261"/>
-      <c r="CG7" s="261"/>
-      <c r="CH7" s="261"/>
-      <c r="CI7" s="261"/>
-      <c r="CJ7" s="261"/>
-      <c r="CK7" s="261"/>
-      <c r="CL7" s="261"/>
-      <c r="CM7" s="261"/>
-      <c r="CN7" s="261"/>
-      <c r="CO7" s="261"/>
-      <c r="CP7" s="261"/>
-      <c r="CQ7" s="261"/>
-      <c r="CR7" s="261"/>
-      <c r="CS7" s="261"/>
-      <c r="CT7" s="261"/>
-      <c r="CU7" s="261"/>
-      <c r="CV7" s="261"/>
-      <c r="CW7" s="261"/>
-      <c r="CX7" s="261"/>
-      <c r="CY7" s="261"/>
-      <c r="CZ7" s="261"/>
-      <c r="DA7" s="261"/>
-      <c r="DB7" s="261"/>
-      <c r="DC7" s="261"/>
-      <c r="DD7" s="261"/>
-      <c r="DE7" s="261"/>
-      <c r="DF7" s="261"/>
-      <c r="DG7" s="261"/>
-      <c r="DH7" s="261"/>
-      <c r="DI7" s="261"/>
-      <c r="DJ7" s="261"/>
-      <c r="DK7" s="261"/>
-      <c r="DL7" s="261"/>
-      <c r="DM7" s="261"/>
-      <c r="DN7" s="261"/>
-      <c r="DO7" s="261"/>
-      <c r="DP7" s="261"/>
-      <c r="DQ7" s="261"/>
-      <c r="DR7" s="261"/>
-      <c r="DS7" s="261"/>
-      <c r="DT7" s="261"/>
-      <c r="DU7" s="261"/>
-      <c r="DV7" s="261"/>
-      <c r="DW7" s="261"/>
-      <c r="DX7" s="261"/>
-      <c r="DY7" s="261"/>
-      <c r="DZ7" s="261"/>
-      <c r="EA7" s="261"/>
-      <c r="EB7" s="261"/>
-      <c r="EC7" s="261"/>
-      <c r="ED7" s="261"/>
-      <c r="EE7" s="261"/>
-      <c r="EF7" s="261"/>
-      <c r="EG7" s="261"/>
-      <c r="EH7" s="261"/>
-      <c r="EI7" s="261"/>
-      <c r="EJ7" s="261"/>
-      <c r="EK7" s="261"/>
-      <c r="EL7" s="261"/>
-      <c r="EM7" s="261"/>
-      <c r="EN7" s="261"/>
-      <c r="EO7" s="261"/>
-      <c r="EP7" s="261"/>
-      <c r="EQ7" s="261"/>
-      <c r="ER7" s="261"/>
-      <c r="ES7" s="261"/>
-      <c r="ET7" s="261"/>
-      <c r="EU7" s="261"/>
-      <c r="EV7" s="261"/>
-      <c r="EW7" s="261"/>
-      <c r="EX7" s="261"/>
-      <c r="EY7" s="261"/>
-      <c r="EZ7" s="261"/>
-      <c r="FA7" s="261"/>
+      <c r="AD7" s="292"/>
+      <c r="AE7" s="293"/>
+      <c r="AF7" s="294"/>
+      <c r="AG7" s="171"/>
+      <c r="AH7" s="171"/>
+      <c r="AI7" s="171"/>
+      <c r="AJ7" s="171"/>
+      <c r="AK7" s="171"/>
+      <c r="AL7" s="171"/>
+      <c r="AM7" s="258"/>
+      <c r="AN7" s="258"/>
+      <c r="AO7" s="258"/>
+      <c r="AP7" s="258"/>
+      <c r="AQ7" s="258"/>
+      <c r="AR7" s="258"/>
+      <c r="AS7" s="258"/>
+      <c r="AT7" s="258"/>
+      <c r="AU7" s="258"/>
+      <c r="AV7" s="258"/>
+      <c r="AW7" s="258"/>
+      <c r="AX7" s="258"/>
+      <c r="AY7" s="258"/>
+      <c r="AZ7" s="258"/>
+      <c r="BA7" s="258"/>
+      <c r="BB7" s="258"/>
+      <c r="BC7" s="258"/>
+      <c r="BD7" s="258"/>
+      <c r="BE7" s="258"/>
+      <c r="BF7" s="258"/>
+      <c r="BG7" s="258"/>
+      <c r="BH7" s="258"/>
+      <c r="BI7" s="258"/>
+      <c r="BJ7" s="258"/>
+      <c r="BK7" s="258"/>
+      <c r="BL7" s="258"/>
+      <c r="BM7" s="258"/>
+      <c r="BN7" s="258"/>
+      <c r="BO7" s="258"/>
+      <c r="BP7" s="258"/>
+      <c r="BQ7" s="258"/>
+      <c r="BR7" s="258"/>
+      <c r="BS7" s="258"/>
+      <c r="BT7" s="258"/>
+      <c r="BU7" s="258"/>
+      <c r="BV7" s="258"/>
+      <c r="BW7" s="258"/>
+      <c r="BX7" s="258"/>
+      <c r="BY7" s="258"/>
+      <c r="BZ7" s="258"/>
+      <c r="CA7" s="258"/>
+      <c r="CB7" s="258"/>
+      <c r="CC7" s="258"/>
+      <c r="CD7" s="258"/>
+      <c r="CE7" s="258"/>
+      <c r="CF7" s="258"/>
+      <c r="CG7" s="258"/>
+      <c r="CH7" s="258"/>
+      <c r="CI7" s="258"/>
+      <c r="CJ7" s="258"/>
+      <c r="CK7" s="258"/>
+      <c r="CL7" s="258"/>
+      <c r="CM7" s="258"/>
+      <c r="CN7" s="258"/>
+      <c r="CO7" s="258"/>
+      <c r="CP7" s="258"/>
+      <c r="CQ7" s="258"/>
+      <c r="CR7" s="258"/>
+      <c r="CS7" s="258"/>
+      <c r="CT7" s="258"/>
+      <c r="CU7" s="258"/>
+      <c r="CV7" s="258"/>
+      <c r="CW7" s="258"/>
+      <c r="CX7" s="258"/>
+      <c r="CY7" s="258"/>
+      <c r="CZ7" s="258"/>
+      <c r="DA7" s="258"/>
+      <c r="DB7" s="258"/>
+      <c r="DC7" s="258"/>
+      <c r="DD7" s="258"/>
+      <c r="DE7" s="258"/>
+      <c r="DF7" s="258"/>
+      <c r="DG7" s="258"/>
+      <c r="DH7" s="258"/>
+      <c r="DI7" s="258"/>
+      <c r="DJ7" s="258"/>
+      <c r="DK7" s="258"/>
+      <c r="DL7" s="258"/>
+      <c r="DM7" s="258"/>
+      <c r="DN7" s="258"/>
+      <c r="DO7" s="258"/>
+      <c r="DP7" s="258"/>
+      <c r="DQ7" s="258"/>
+      <c r="DR7" s="258"/>
+      <c r="DS7" s="258"/>
+      <c r="DT7" s="258"/>
+      <c r="DU7" s="258"/>
+      <c r="DV7" s="258"/>
+      <c r="DW7" s="258"/>
+      <c r="DX7" s="258"/>
+      <c r="DY7" s="258"/>
+      <c r="DZ7" s="258"/>
+      <c r="EA7" s="258"/>
+      <c r="EB7" s="258"/>
+      <c r="EC7" s="258"/>
+      <c r="ED7" s="258"/>
+      <c r="EE7" s="258"/>
+      <c r="EF7" s="258"/>
+      <c r="EG7" s="258"/>
+      <c r="EH7" s="258"/>
+      <c r="EI7" s="258"/>
+      <c r="EJ7" s="258"/>
+      <c r="EK7" s="258"/>
+      <c r="EL7" s="258"/>
+      <c r="EM7" s="258"/>
+      <c r="EN7" s="258"/>
+      <c r="EO7" s="258"/>
+      <c r="EP7" s="258"/>
+      <c r="EQ7" s="258"/>
+      <c r="ER7" s="258"/>
+      <c r="ES7" s="258"/>
+      <c r="ET7" s="258"/>
+      <c r="EU7" s="258"/>
+      <c r="EV7" s="258"/>
+      <c r="EW7" s="258"/>
+      <c r="EX7" s="258"/>
+      <c r="EY7" s="258"/>
+      <c r="EZ7" s="258"/>
+      <c r="FA7" s="258"/>
       <c r="FJ7" s="22"/>
       <c r="FK7" s="22"/>
       <c r="FP7" s="1"/>
@@ -5751,9 +5801,9 @@
       <c r="FS8" s="1"/>
     </row>
     <row r="9" spans="1:175" s="17" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="271"/>
-      <c r="B9" s="272"/>
-      <c r="C9" s="273"/>
+      <c r="A9" s="268"/>
+      <c r="B9" s="269"/>
+      <c r="C9" s="270"/>
       <c r="D9" s="36"/>
       <c r="E9" s="77"/>
       <c r="F9" s="77"/>
@@ -5909,11 +5959,11 @@
       <c r="EZ9" s="18"/>
     </row>
     <row r="10" spans="1:175" s="17" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="274" t="s">
+      <c r="A10" s="271" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="275"/>
-      <c r="C10" s="276"/>
+      <c r="B10" s="272"/>
+      <c r="C10" s="273"/>
       <c r="D10" s="68"/>
       <c r="E10" s="67"/>
       <c r="F10" s="67"/>
@@ -5952,11 +6002,11 @@
       <c r="AM10" s="69"/>
     </row>
     <row r="11" spans="1:175" s="17" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="277" t="s">
+      <c r="A11" s="274" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="278"/>
-      <c r="C11" s="279"/>
+      <c r="B11" s="275"/>
+      <c r="C11" s="276"/>
       <c r="D11" s="70"/>
       <c r="E11" s="64"/>
       <c r="F11" s="64"/>
@@ -5995,11 +6045,11 @@
       <c r="AM11" s="71"/>
     </row>
     <row r="12" spans="1:175" s="17" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="280" t="s">
+      <c r="A12" s="277" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="281"/>
-      <c r="C12" s="282"/>
+      <c r="B12" s="278"/>
+      <c r="C12" s="279"/>
       <c r="D12" s="72"/>
       <c r="E12" s="33"/>
       <c r="F12" s="33"/>
@@ -6038,11 +6088,11 @@
       <c r="AM12" s="34"/>
     </row>
     <row r="13" spans="1:175" s="17" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="226" t="s">
+      <c r="A13" s="232" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="227"/>
-      <c r="C13" s="228"/>
+      <c r="B13" s="233"/>
+      <c r="C13" s="234"/>
       <c r="D13" s="70"/>
       <c r="E13" s="64"/>
       <c r="F13" s="64"/>
@@ -6081,11 +6131,11 @@
       <c r="AM13" s="71"/>
     </row>
     <row r="14" spans="1:175" s="17" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="234" t="s">
+      <c r="A14" s="240" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="235"/>
-      <c r="C14" s="236"/>
+      <c r="B14" s="241"/>
+      <c r="C14" s="242"/>
       <c r="D14" s="72"/>
       <c r="E14" s="33"/>
       <c r="F14" s="33"/>
@@ -6124,11 +6174,11 @@
       <c r="AM14" s="34"/>
     </row>
     <row r="15" spans="1:175" s="17" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="237" t="s">
+      <c r="A15" s="243" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="238"/>
-      <c r="C15" s="248"/>
+      <c r="B15" s="244"/>
+      <c r="C15" s="254"/>
       <c r="D15" s="73"/>
       <c r="E15" s="65"/>
       <c r="F15" s="65"/>
@@ -6167,11 +6217,11 @@
       <c r="AM15" s="74"/>
     </row>
     <row r="16" spans="1:175" s="17" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="239" t="s">
+      <c r="A16" s="245" t="s">
         <v>178</v>
       </c>
-      <c r="B16" s="240"/>
-      <c r="C16" s="241"/>
+      <c r="B16" s="246"/>
+      <c r="C16" s="247"/>
       <c r="D16" s="75"/>
       <c r="E16" s="66"/>
       <c r="F16" s="66"/>
@@ -6210,54 +6260,54 @@
       <c r="AM16" s="94"/>
     </row>
     <row r="17" spans="1:175" s="17" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="242" t="s">
+      <c r="A17" s="248" t="s">
         <v>186</v>
       </c>
-      <c r="B17" s="243"/>
-      <c r="C17" s="244"/>
-      <c r="D17" s="283"/>
-      <c r="E17" s="284"/>
-      <c r="F17" s="284"/>
-      <c r="G17" s="284"/>
-      <c r="H17" s="284"/>
-      <c r="I17" s="284"/>
-      <c r="J17" s="284"/>
-      <c r="K17" s="284"/>
-      <c r="L17" s="284"/>
-      <c r="M17" s="284"/>
-      <c r="N17" s="284"/>
-      <c r="O17" s="285"/>
-      <c r="P17" s="283"/>
-      <c r="Q17" s="284"/>
-      <c r="R17" s="284"/>
-      <c r="S17" s="284"/>
-      <c r="T17" s="284"/>
-      <c r="U17" s="284"/>
-      <c r="V17" s="284"/>
-      <c r="W17" s="284"/>
-      <c r="X17" s="284"/>
-      <c r="Y17" s="284"/>
-      <c r="Z17" s="284"/>
-      <c r="AA17" s="285"/>
-      <c r="AB17" s="283"/>
-      <c r="AC17" s="284"/>
-      <c r="AD17" s="284"/>
-      <c r="AE17" s="284"/>
-      <c r="AF17" s="284"/>
-      <c r="AG17" s="284"/>
-      <c r="AH17" s="284"/>
-      <c r="AI17" s="284"/>
-      <c r="AJ17" s="284"/>
-      <c r="AK17" s="284"/>
-      <c r="AL17" s="284"/>
-      <c r="AM17" s="285"/>
+      <c r="B17" s="249"/>
+      <c r="C17" s="250"/>
+      <c r="D17" s="166"/>
+      <c r="E17" s="167"/>
+      <c r="F17" s="167"/>
+      <c r="G17" s="167"/>
+      <c r="H17" s="167"/>
+      <c r="I17" s="167"/>
+      <c r="J17" s="167"/>
+      <c r="K17" s="167"/>
+      <c r="L17" s="167"/>
+      <c r="M17" s="167"/>
+      <c r="N17" s="167"/>
+      <c r="O17" s="168"/>
+      <c r="P17" s="166"/>
+      <c r="Q17" s="167"/>
+      <c r="R17" s="167"/>
+      <c r="S17" s="167"/>
+      <c r="T17" s="167"/>
+      <c r="U17" s="167"/>
+      <c r="V17" s="167"/>
+      <c r="W17" s="167"/>
+      <c r="X17" s="167"/>
+      <c r="Y17" s="167"/>
+      <c r="Z17" s="167"/>
+      <c r="AA17" s="168"/>
+      <c r="AB17" s="166"/>
+      <c r="AC17" s="167"/>
+      <c r="AD17" s="167"/>
+      <c r="AE17" s="167"/>
+      <c r="AF17" s="167"/>
+      <c r="AG17" s="167"/>
+      <c r="AH17" s="167"/>
+      <c r="AI17" s="167"/>
+      <c r="AJ17" s="167"/>
+      <c r="AK17" s="167"/>
+      <c r="AL17" s="167"/>
+      <c r="AM17" s="168"/>
     </row>
     <row r="18" spans="1:175" s="17" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="166" t="s">
+      <c r="A18" s="172" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="167"/>
-      <c r="C18" s="168"/>
+      <c r="B18" s="173"/>
+      <c r="C18" s="174"/>
       <c r="D18" s="70"/>
       <c r="E18" s="64"/>
       <c r="F18" s="64"/>
@@ -6296,11 +6346,11 @@
       <c r="AM18" s="71"/>
     </row>
     <row r="19" spans="1:175" s="17" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="169" t="s">
+      <c r="A19" s="175" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="170"/>
-      <c r="C19" s="171"/>
+      <c r="B19" s="176"/>
+      <c r="C19" s="177"/>
       <c r="D19" s="76"/>
       <c r="E19" s="47"/>
       <c r="F19" s="47"/>
@@ -6339,9 +6389,9 @@
       <c r="AM19" s="48"/>
     </row>
     <row r="20" spans="1:175" s="19" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="220"/>
-      <c r="B20" s="221"/>
-      <c r="C20" s="222"/>
+      <c r="A20" s="226"/>
+      <c r="B20" s="227"/>
+      <c r="C20" s="228"/>
       <c r="D20" s="99"/>
       <c r="E20" s="100"/>
       <c r="F20" s="100"/>
@@ -6380,11 +6430,11 @@
       <c r="AM20" s="151"/>
     </row>
     <row r="21" spans="1:175" s="17" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="223" t="s">
+      <c r="A21" s="229" t="s">
         <v>2</v>
       </c>
-      <c r="B21" s="224"/>
-      <c r="C21" s="225"/>
+      <c r="B21" s="230"/>
+      <c r="C21" s="231"/>
       <c r="D21" s="68"/>
       <c r="E21" s="67"/>
       <c r="F21" s="67"/>
@@ -6423,11 +6473,11 @@
       <c r="AM21" s="69"/>
     </row>
     <row r="22" spans="1:175" s="17" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="226" t="s">
+      <c r="A22" s="232" t="s">
         <v>3</v>
       </c>
-      <c r="B22" s="227"/>
-      <c r="C22" s="228"/>
+      <c r="B22" s="233"/>
+      <c r="C22" s="234"/>
       <c r="D22" s="70"/>
       <c r="E22" s="64"/>
       <c r="F22" s="64"/>
@@ -6466,11 +6516,11 @@
       <c r="AM22" s="71"/>
     </row>
     <row r="23" spans="1:175" s="17" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="234" t="s">
+      <c r="A23" s="240" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="235"/>
-      <c r="C23" s="236"/>
+      <c r="B23" s="241"/>
+      <c r="C23" s="242"/>
       <c r="D23" s="72"/>
       <c r="E23" s="33"/>
       <c r="F23" s="33"/>
@@ -6509,11 +6559,11 @@
       <c r="AM23" s="34"/>
     </row>
     <row r="24" spans="1:175" s="17" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="226" t="s">
+      <c r="A24" s="232" t="s">
         <v>5</v>
       </c>
-      <c r="B24" s="227"/>
-      <c r="C24" s="228"/>
+      <c r="B24" s="233"/>
+      <c r="C24" s="234"/>
       <c r="D24" s="70"/>
       <c r="E24" s="64"/>
       <c r="F24" s="64"/>
@@ -6552,11 +6602,11 @@
       <c r="AM24" s="71"/>
     </row>
     <row r="25" spans="1:175" s="17" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="234" t="s">
+      <c r="A25" s="240" t="s">
         <v>17</v>
       </c>
-      <c r="B25" s="235"/>
-      <c r="C25" s="236"/>
+      <c r="B25" s="241"/>
+      <c r="C25" s="242"/>
       <c r="D25" s="72"/>
       <c r="E25" s="33"/>
       <c r="F25" s="33"/>
@@ -6595,11 +6645,11 @@
       <c r="AM25" s="34"/>
     </row>
     <row r="26" spans="1:175" s="17" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="237" t="s">
+      <c r="A26" s="243" t="s">
         <v>6</v>
       </c>
-      <c r="B26" s="238"/>
-      <c r="C26" s="238"/>
+      <c r="B26" s="244"/>
+      <c r="C26" s="244"/>
       <c r="D26" s="73"/>
       <c r="E26" s="65"/>
       <c r="F26" s="65"/>
@@ -6638,11 +6688,11 @@
       <c r="AM26" s="74"/>
     </row>
     <row r="27" spans="1:175" s="17" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="239" t="s">
+      <c r="A27" s="245" t="s">
         <v>178</v>
       </c>
-      <c r="B27" s="240"/>
-      <c r="C27" s="241"/>
+      <c r="B27" s="246"/>
+      <c r="C27" s="247"/>
       <c r="D27" s="75"/>
       <c r="E27" s="66"/>
       <c r="F27" s="66"/>
@@ -6681,54 +6731,54 @@
       <c r="AM27" s="94"/>
     </row>
     <row r="28" spans="1:175" s="17" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="242" t="s">
+      <c r="A28" s="248" t="s">
         <v>186</v>
       </c>
-      <c r="B28" s="243"/>
-      <c r="C28" s="244"/>
-      <c r="D28" s="286"/>
-      <c r="E28" s="284"/>
-      <c r="F28" s="284"/>
-      <c r="G28" s="284"/>
-      <c r="H28" s="284"/>
-      <c r="I28" s="284"/>
-      <c r="J28" s="284"/>
-      <c r="K28" s="284"/>
-      <c r="L28" s="284"/>
-      <c r="M28" s="284"/>
-      <c r="N28" s="284"/>
-      <c r="O28" s="285"/>
-      <c r="P28" s="283"/>
-      <c r="Q28" s="284"/>
-      <c r="R28" s="284"/>
-      <c r="S28" s="284"/>
-      <c r="T28" s="284"/>
-      <c r="U28" s="284"/>
-      <c r="V28" s="284"/>
-      <c r="W28" s="284"/>
-      <c r="X28" s="284"/>
-      <c r="Y28" s="284"/>
-      <c r="Z28" s="284"/>
-      <c r="AA28" s="285"/>
-      <c r="AB28" s="283"/>
-      <c r="AC28" s="284"/>
-      <c r="AD28" s="284"/>
-      <c r="AE28" s="284"/>
-      <c r="AF28" s="284"/>
-      <c r="AG28" s="284"/>
-      <c r="AH28" s="284"/>
-      <c r="AI28" s="284"/>
-      <c r="AJ28" s="284"/>
-      <c r="AK28" s="284"/>
-      <c r="AL28" s="284"/>
-      <c r="AM28" s="285"/>
+      <c r="B28" s="249"/>
+      <c r="C28" s="250"/>
+      <c r="D28" s="169"/>
+      <c r="E28" s="167"/>
+      <c r="F28" s="167"/>
+      <c r="G28" s="167"/>
+      <c r="H28" s="167"/>
+      <c r="I28" s="167"/>
+      <c r="J28" s="167"/>
+      <c r="K28" s="167"/>
+      <c r="L28" s="167"/>
+      <c r="M28" s="167"/>
+      <c r="N28" s="167"/>
+      <c r="O28" s="168"/>
+      <c r="P28" s="166"/>
+      <c r="Q28" s="167"/>
+      <c r="R28" s="167"/>
+      <c r="S28" s="167"/>
+      <c r="T28" s="167"/>
+      <c r="U28" s="167"/>
+      <c r="V28" s="167"/>
+      <c r="W28" s="167"/>
+      <c r="X28" s="167"/>
+      <c r="Y28" s="167"/>
+      <c r="Z28" s="167"/>
+      <c r="AA28" s="168"/>
+      <c r="AB28" s="166"/>
+      <c r="AC28" s="167"/>
+      <c r="AD28" s="167"/>
+      <c r="AE28" s="167"/>
+      <c r="AF28" s="167"/>
+      <c r="AG28" s="167"/>
+      <c r="AH28" s="167"/>
+      <c r="AI28" s="167"/>
+      <c r="AJ28" s="167"/>
+      <c r="AK28" s="167"/>
+      <c r="AL28" s="167"/>
+      <c r="AM28" s="168"/>
     </row>
     <row r="29" spans="1:175" s="17" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="166" t="s">
+      <c r="A29" s="172" t="s">
         <v>7</v>
       </c>
-      <c r="B29" s="167"/>
-      <c r="C29" s="168"/>
+      <c r="B29" s="173"/>
+      <c r="C29" s="174"/>
       <c r="D29" s="70"/>
       <c r="E29" s="64"/>
       <c r="F29" s="64"/>
@@ -6767,11 +6817,11 @@
       <c r="AM29" s="71"/>
     </row>
     <row r="30" spans="1:175" s="17" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="169" t="s">
+      <c r="A30" s="175" t="s">
         <v>1</v>
       </c>
-      <c r="B30" s="170"/>
-      <c r="C30" s="171"/>
+      <c r="B30" s="176"/>
+      <c r="C30" s="177"/>
       <c r="D30" s="76"/>
       <c r="E30" s="47"/>
       <c r="F30" s="47"/>
@@ -7027,44 +7077,44 @@
       <c r="FS32" s="1"/>
     </row>
     <row r="33" spans="1:179" s="5" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="231" t="s">
+      <c r="A33" s="237" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="232"/>
-      <c r="C33" s="232"/>
-      <c r="D33" s="232"/>
-      <c r="E33" s="232"/>
-      <c r="F33" s="232"/>
-      <c r="G33" s="232"/>
-      <c r="H33" s="232"/>
-      <c r="I33" s="232"/>
-      <c r="J33" s="232"/>
-      <c r="K33" s="232"/>
-      <c r="L33" s="233"/>
+      <c r="B33" s="238"/>
+      <c r="C33" s="238"/>
+      <c r="D33" s="238"/>
+      <c r="E33" s="238"/>
+      <c r="F33" s="238"/>
+      <c r="G33" s="238"/>
+      <c r="H33" s="238"/>
+      <c r="I33" s="238"/>
+      <c r="J33" s="238"/>
+      <c r="K33" s="238"/>
+      <c r="L33" s="239"/>
       <c r="M33" s="62"/>
       <c r="N33" s="62"/>
       <c r="O33" s="62"/>
       <c r="P33" s="63"/>
       <c r="Q33" s="63"/>
-      <c r="R33" s="172" t="s">
+      <c r="R33" s="178" t="s">
         <v>97</v>
       </c>
-      <c r="S33" s="172"/>
-      <c r="T33" s="172"/>
-      <c r="U33" s="172"/>
-      <c r="V33" s="172"/>
-      <c r="W33" s="172"/>
-      <c r="X33" s="172"/>
-      <c r="Y33" s="172"/>
-      <c r="Z33" s="172"/>
-      <c r="AA33" s="172"/>
-      <c r="AB33" s="172"/>
-      <c r="AC33" s="172"/>
-      <c r="AD33" s="172"/>
-      <c r="AE33" s="172"/>
-      <c r="AF33" s="172"/>
-      <c r="AG33" s="172"/>
-      <c r="AH33" s="172"/>
+      <c r="S33" s="178"/>
+      <c r="T33" s="178"/>
+      <c r="U33" s="178"/>
+      <c r="V33" s="178"/>
+      <c r="W33" s="178"/>
+      <c r="X33" s="178"/>
+      <c r="Y33" s="178"/>
+      <c r="Z33" s="178"/>
+      <c r="AA33" s="178"/>
+      <c r="AB33" s="178"/>
+      <c r="AC33" s="178"/>
+      <c r="AD33" s="178"/>
+      <c r="AE33" s="178"/>
+      <c r="AF33" s="178"/>
+      <c r="AG33" s="178"/>
+      <c r="AH33" s="178"/>
       <c r="AI33" s="63"/>
       <c r="AJ33" s="63"/>
       <c r="AK33" s="63"/>
@@ -7220,23 +7270,23 @@
       <c r="L34" s="79"/>
       <c r="P34" s="92"/>
       <c r="Q34" s="92"/>
-      <c r="R34" s="172"/>
-      <c r="S34" s="172"/>
-      <c r="T34" s="172"/>
-      <c r="U34" s="172"/>
-      <c r="V34" s="172"/>
-      <c r="W34" s="172"/>
-      <c r="X34" s="172"/>
-      <c r="Y34" s="172"/>
-      <c r="Z34" s="172"/>
-      <c r="AA34" s="172"/>
-      <c r="AB34" s="172"/>
-      <c r="AC34" s="172"/>
-      <c r="AD34" s="172"/>
-      <c r="AE34" s="172"/>
-      <c r="AF34" s="172"/>
-      <c r="AG34" s="172"/>
-      <c r="AH34" s="172"/>
+      <c r="R34" s="178"/>
+      <c r="S34" s="178"/>
+      <c r="T34" s="178"/>
+      <c r="U34" s="178"/>
+      <c r="V34" s="178"/>
+      <c r="W34" s="178"/>
+      <c r="X34" s="178"/>
+      <c r="Y34" s="178"/>
+      <c r="Z34" s="178"/>
+      <c r="AA34" s="178"/>
+      <c r="AB34" s="178"/>
+      <c r="AC34" s="178"/>
+      <c r="AD34" s="178"/>
+      <c r="AE34" s="178"/>
+      <c r="AF34" s="178"/>
+      <c r="AG34" s="178"/>
+      <c r="AH34" s="178"/>
       <c r="AI34" s="92"/>
       <c r="AJ34" s="92"/>
       <c r="AK34" s="92"/>
@@ -7272,32 +7322,32 @@
       <c r="L35" s="80"/>
       <c r="P35" s="92"/>
       <c r="Q35" s="92"/>
-      <c r="R35" s="173" t="s">
+      <c r="R35" s="179" t="s">
         <v>102</v>
       </c>
-      <c r="S35" s="174"/>
-      <c r="T35" s="177" t="s">
+      <c r="S35" s="180"/>
+      <c r="T35" s="183" t="s">
         <v>60</v>
       </c>
-      <c r="U35" s="179" t="s">
+      <c r="U35" s="185" t="s">
         <v>61</v>
       </c>
-      <c r="V35" s="180" t="s">
+      <c r="V35" s="186" t="s">
         <v>62</v>
       </c>
-      <c r="W35" s="181" t="s">
+      <c r="W35" s="187" t="s">
         <v>98</v>
       </c>
-      <c r="X35" s="181"/>
-      <c r="Y35" s="181"/>
-      <c r="Z35" s="181"/>
-      <c r="AA35" s="184" t="s">
+      <c r="X35" s="187"/>
+      <c r="Y35" s="187"/>
+      <c r="Z35" s="187"/>
+      <c r="AA35" s="190" t="s">
         <v>100</v>
       </c>
-      <c r="AB35" s="183" t="s">
+      <c r="AB35" s="189" t="s">
         <v>99</v>
       </c>
-      <c r="AC35" s="183"/>
+      <c r="AC35" s="189"/>
       <c r="AD35" s="102"/>
       <c r="AE35" s="103"/>
       <c r="AF35" s="103"/>
@@ -7338,18 +7388,18 @@
       <c r="L36" s="80"/>
       <c r="P36" s="92"/>
       <c r="Q36" s="92"/>
-      <c r="R36" s="175"/>
-      <c r="S36" s="176"/>
-      <c r="T36" s="245"/>
-      <c r="U36" s="246"/>
-      <c r="V36" s="247"/>
-      <c r="W36" s="182"/>
-      <c r="X36" s="182"/>
-      <c r="Y36" s="182"/>
-      <c r="Z36" s="182"/>
-      <c r="AA36" s="229"/>
-      <c r="AB36" s="230"/>
-      <c r="AC36" s="230"/>
+      <c r="R36" s="181"/>
+      <c r="S36" s="182"/>
+      <c r="T36" s="251"/>
+      <c r="U36" s="252"/>
+      <c r="V36" s="253"/>
+      <c r="W36" s="188"/>
+      <c r="X36" s="188"/>
+      <c r="Y36" s="188"/>
+      <c r="Z36" s="188"/>
+      <c r="AA36" s="235"/>
+      <c r="AB36" s="236"/>
+      <c r="AC36" s="236"/>
       <c r="AD36" s="104"/>
       <c r="AE36" s="105"/>
       <c r="AF36" s="105"/>
@@ -7384,33 +7434,33 @@
       <c r="L37" s="80"/>
       <c r="P37" s="92"/>
       <c r="Q37" s="92"/>
-      <c r="R37" s="173" t="s">
+      <c r="R37" s="179" t="s">
         <v>66</v>
       </c>
-      <c r="S37" s="174"/>
-      <c r="T37" s="177" t="s">
+      <c r="S37" s="180"/>
+      <c r="T37" s="183" t="s">
         <v>67</v>
       </c>
-      <c r="U37" s="178" t="s">
+      <c r="U37" s="184" t="s">
         <v>101</v>
       </c>
-      <c r="V37" s="179"/>
-      <c r="W37" s="180" t="s">
+      <c r="V37" s="185"/>
+      <c r="W37" s="186" t="s">
         <v>69</v>
       </c>
-      <c r="X37" s="181" t="s">
+      <c r="X37" s="187" t="s">
         <v>63</v>
       </c>
-      <c r="Y37" s="181"/>
-      <c r="Z37" s="181"/>
-      <c r="AA37" s="181"/>
-      <c r="AB37" s="184" t="s">
+      <c r="Y37" s="187"/>
+      <c r="Z37" s="187"/>
+      <c r="AA37" s="187"/>
+      <c r="AB37" s="190" t="s">
         <v>64</v>
       </c>
-      <c r="AC37" s="183" t="s">
+      <c r="AC37" s="189" t="s">
         <v>65</v>
       </c>
-      <c r="AD37" s="183"/>
+      <c r="AD37" s="189"/>
       <c r="AE37" s="105"/>
       <c r="AF37" s="105"/>
       <c r="AG37" s="105"/>
@@ -7444,19 +7494,19 @@
       <c r="L38" s="80"/>
       <c r="P38" s="92"/>
       <c r="Q38" s="92"/>
-      <c r="R38" s="175"/>
-      <c r="S38" s="176"/>
-      <c r="T38" s="177"/>
-      <c r="U38" s="179"/>
-      <c r="V38" s="179"/>
-      <c r="W38" s="180"/>
-      <c r="X38" s="181"/>
-      <c r="Y38" s="181"/>
-      <c r="Z38" s="181"/>
-      <c r="AA38" s="181"/>
-      <c r="AB38" s="184"/>
-      <c r="AC38" s="183"/>
-      <c r="AD38" s="183"/>
+      <c r="R38" s="181"/>
+      <c r="S38" s="182"/>
+      <c r="T38" s="183"/>
+      <c r="U38" s="185"/>
+      <c r="V38" s="185"/>
+      <c r="W38" s="186"/>
+      <c r="X38" s="187"/>
+      <c r="Y38" s="187"/>
+      <c r="Z38" s="187"/>
+      <c r="AA38" s="187"/>
+      <c r="AB38" s="190"/>
+      <c r="AC38" s="189"/>
+      <c r="AD38" s="189"/>
       <c r="AE38" s="103"/>
       <c r="AF38" s="103"/>
       <c r="AG38" s="103"/>
@@ -7490,39 +7540,39 @@
       <c r="L39" s="80"/>
       <c r="P39" s="92"/>
       <c r="Q39" s="92"/>
-      <c r="R39" s="173" t="s">
+      <c r="R39" s="179" t="s">
         <v>70</v>
       </c>
-      <c r="S39" s="174"/>
-      <c r="T39" s="177" t="s">
+      <c r="S39" s="180"/>
+      <c r="T39" s="183" t="s">
         <v>67</v>
       </c>
-      <c r="U39" s="179" t="s">
+      <c r="U39" s="185" t="s">
         <v>68</v>
       </c>
-      <c r="V39" s="179"/>
-      <c r="W39" s="219" t="s">
+      <c r="V39" s="185"/>
+      <c r="W39" s="225" t="s">
         <v>71</v>
       </c>
-      <c r="X39" s="219"/>
-      <c r="Y39" s="219"/>
-      <c r="Z39" s="219"/>
-      <c r="AA39" s="180" t="s">
+      <c r="X39" s="225"/>
+      <c r="Y39" s="225"/>
+      <c r="Z39" s="225"/>
+      <c r="AA39" s="186" t="s">
         <v>69</v>
       </c>
-      <c r="AB39" s="181" t="s">
+      <c r="AB39" s="187" t="s">
         <v>63</v>
       </c>
-      <c r="AC39" s="181"/>
-      <c r="AD39" s="181"/>
-      <c r="AE39" s="181"/>
-      <c r="AF39" s="184" t="s">
+      <c r="AC39" s="187"/>
+      <c r="AD39" s="187"/>
+      <c r="AE39" s="187"/>
+      <c r="AF39" s="190" t="s">
         <v>64</v>
       </c>
-      <c r="AG39" s="183" t="s">
+      <c r="AG39" s="189" t="s">
         <v>65</v>
       </c>
-      <c r="AH39" s="183"/>
+      <c r="AH39" s="189"/>
       <c r="AI39" s="92"/>
       <c r="AJ39" s="92"/>
       <c r="AK39" s="92"/>
@@ -7561,23 +7611,23 @@
       <c r="O40" s="92"/>
       <c r="P40" s="92"/>
       <c r="Q40" s="92"/>
-      <c r="R40" s="175"/>
-      <c r="S40" s="176"/>
-      <c r="T40" s="177"/>
-      <c r="U40" s="179"/>
-      <c r="V40" s="179"/>
-      <c r="W40" s="219"/>
-      <c r="X40" s="219"/>
-      <c r="Y40" s="219"/>
-      <c r="Z40" s="219"/>
-      <c r="AA40" s="180"/>
-      <c r="AB40" s="181"/>
-      <c r="AC40" s="181"/>
-      <c r="AD40" s="181"/>
-      <c r="AE40" s="181"/>
-      <c r="AF40" s="184"/>
-      <c r="AG40" s="183"/>
-      <c r="AH40" s="183"/>
+      <c r="R40" s="181"/>
+      <c r="S40" s="182"/>
+      <c r="T40" s="183"/>
+      <c r="U40" s="185"/>
+      <c r="V40" s="185"/>
+      <c r="W40" s="225"/>
+      <c r="X40" s="225"/>
+      <c r="Y40" s="225"/>
+      <c r="Z40" s="225"/>
+      <c r="AA40" s="186"/>
+      <c r="AB40" s="187"/>
+      <c r="AC40" s="187"/>
+      <c r="AD40" s="187"/>
+      <c r="AE40" s="187"/>
+      <c r="AF40" s="190"/>
+      <c r="AG40" s="189"/>
+      <c r="AH40" s="189"/>
       <c r="AI40" s="92"/>
       <c r="AJ40" s="92"/>
       <c r="AK40" s="92"/>
@@ -7860,31 +7910,31 @@
       <c r="S44" s="142" t="s">
         <v>75</v>
       </c>
-      <c r="T44" s="215" t="s">
+      <c r="T44" s="221" t="s">
         <v>14</v>
       </c>
-      <c r="U44" s="216"/>
-      <c r="V44" s="216"/>
+      <c r="U44" s="222"/>
+      <c r="V44" s="222"/>
       <c r="W44" s="142" t="s">
         <v>76</v>
       </c>
       <c r="X44" s="142" t="s">
         <v>77</v>
       </c>
-      <c r="Y44" s="218" t="s">
+      <c r="Y44" s="224" t="s">
         <v>78</v>
       </c>
-      <c r="Z44" s="218"/>
-      <c r="AA44" s="215" t="s">
+      <c r="Z44" s="224"/>
+      <c r="AA44" s="221" t="s">
         <v>79</v>
       </c>
-      <c r="AB44" s="216"/>
-      <c r="AC44" s="215" t="s">
+      <c r="AB44" s="222"/>
+      <c r="AC44" s="221" t="s">
         <v>80</v>
       </c>
-      <c r="AD44" s="216"/>
-      <c r="AE44" s="216"/>
-      <c r="AF44" s="217"/>
+      <c r="AD44" s="222"/>
+      <c r="AE44" s="222"/>
+      <c r="AF44" s="223"/>
       <c r="AG44" s="92"/>
       <c r="AH44" s="92"/>
     </row>
@@ -7909,31 +7959,31 @@
       <c r="S45" s="118">
         <v>0</v>
       </c>
-      <c r="T45" s="208" t="s">
+      <c r="T45" s="214" t="s">
         <v>81</v>
       </c>
-      <c r="U45" s="209"/>
-      <c r="V45" s="210"/>
+      <c r="U45" s="215"/>
+      <c r="V45" s="216"/>
       <c r="W45" s="118" t="s">
         <v>82</v>
       </c>
       <c r="X45" s="119" t="s">
         <v>83</v>
       </c>
-      <c r="Y45" s="206" t="s">
+      <c r="Y45" s="212" t="s">
         <v>9</v>
       </c>
-      <c r="Z45" s="206"/>
-      <c r="AA45" s="211" t="s">
+      <c r="Z45" s="212"/>
+      <c r="AA45" s="217" t="s">
         <v>103</v>
       </c>
-      <c r="AB45" s="211"/>
-      <c r="AC45" s="212" t="s">
+      <c r="AB45" s="217"/>
+      <c r="AC45" s="218" t="s">
         <v>84</v>
       </c>
-      <c r="AD45" s="213"/>
-      <c r="AE45" s="213"/>
-      <c r="AF45" s="214"/>
+      <c r="AD45" s="219"/>
+      <c r="AE45" s="219"/>
+      <c r="AF45" s="220"/>
       <c r="AG45" s="92"/>
       <c r="AH45" s="92"/>
     </row>
@@ -7953,37 +8003,37 @@
       <c r="M46" s="63"/>
       <c r="N46" s="63"/>
       <c r="O46" s="63"/>
-      <c r="R46" s="185" t="s">
+      <c r="R46" s="191" t="s">
         <v>85</v>
       </c>
-      <c r="S46" s="187">
+      <c r="S46" s="193">
         <v>15</v>
       </c>
-      <c r="T46" s="189" t="s">
+      <c r="T46" s="195" t="s">
         <v>86</v>
       </c>
-      <c r="U46" s="190"/>
-      <c r="V46" s="191"/>
-      <c r="W46" s="192" t="s">
+      <c r="U46" s="196"/>
+      <c r="V46" s="197"/>
+      <c r="W46" s="198" t="s">
         <v>87</v>
       </c>
       <c r="X46" s="120" t="s">
         <v>83</v>
       </c>
-      <c r="Y46" s="194" t="s">
+      <c r="Y46" s="200" t="s">
         <v>9</v>
       </c>
-      <c r="Z46" s="194"/>
-      <c r="AA46" s="194" t="s">
+      <c r="Z46" s="200"/>
+      <c r="AA46" s="200" t="s">
         <v>88</v>
       </c>
-      <c r="AB46" s="194"/>
-      <c r="AC46" s="195" t="s">
+      <c r="AB46" s="200"/>
+      <c r="AC46" s="201" t="s">
         <v>89</v>
       </c>
-      <c r="AD46" s="196"/>
-      <c r="AE46" s="196"/>
-      <c r="AF46" s="197"/>
+      <c r="AD46" s="202"/>
+      <c r="AE46" s="202"/>
+      <c r="AF46" s="203"/>
       <c r="AI46" s="63"/>
       <c r="AJ46" s="63"/>
       <c r="AK46" s="63"/>
@@ -8127,48 +8177,48 @@
       <c r="FS46" s="1"/>
     </row>
     <row r="47" spans="1:179" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="258" t="s">
+      <c r="A47" s="255" t="s">
         <v>15</v>
       </c>
-      <c r="B47" s="259"/>
-      <c r="C47" s="259"/>
-      <c r="D47" s="259"/>
-      <c r="E47" s="259"/>
-      <c r="F47" s="259"/>
-      <c r="G47" s="259"/>
-      <c r="H47" s="259"/>
-      <c r="I47" s="259"/>
-      <c r="J47" s="259"/>
-      <c r="K47" s="259"/>
-      <c r="L47" s="260"/>
+      <c r="B47" s="256"/>
+      <c r="C47" s="256"/>
+      <c r="D47" s="256"/>
+      <c r="E47" s="256"/>
+      <c r="F47" s="256"/>
+      <c r="G47" s="256"/>
+      <c r="H47" s="256"/>
+      <c r="I47" s="256"/>
+      <c r="J47" s="256"/>
+      <c r="K47" s="256"/>
+      <c r="L47" s="257"/>
       <c r="M47" s="63"/>
       <c r="N47" s="63"/>
       <c r="O47" s="63"/>
-      <c r="R47" s="186"/>
-      <c r="S47" s="188"/>
-      <c r="T47" s="198" t="s">
+      <c r="R47" s="192"/>
+      <c r="S47" s="194"/>
+      <c r="T47" s="204" t="s">
         <v>90</v>
       </c>
-      <c r="U47" s="199"/>
-      <c r="V47" s="200"/>
-      <c r="W47" s="193"/>
+      <c r="U47" s="205"/>
+      <c r="V47" s="206"/>
+      <c r="W47" s="199"/>
       <c r="X47" s="121" t="s">
         <v>91</v>
       </c>
-      <c r="Y47" s="207" t="s">
+      <c r="Y47" s="213" t="s">
         <v>96</v>
       </c>
-      <c r="Z47" s="207"/>
-      <c r="AA47" s="201" t="s">
+      <c r="Z47" s="213"/>
+      <c r="AA47" s="207" t="s">
         <v>92</v>
       </c>
-      <c r="AB47" s="202"/>
-      <c r="AC47" s="203" t="s">
+      <c r="AB47" s="208"/>
+      <c r="AC47" s="209" t="s">
         <v>93</v>
       </c>
-      <c r="AD47" s="204"/>
-      <c r="AE47" s="204"/>
-      <c r="AF47" s="205"/>
+      <c r="AD47" s="210"/>
+      <c r="AE47" s="210"/>
+      <c r="AF47" s="211"/>
       <c r="AI47" s="63"/>
       <c r="AJ47" s="63"/>
       <c r="AK47" s="63"/>
@@ -10488,10 +10538,7 @@
       <headerFooter scaleWithDoc="0" alignWithMargins="0"/>
     </customSheetView>
   </customSheetViews>
-  <mergeCells count="76">
-    <mergeCell ref="AD1:AF7"/>
-    <mergeCell ref="AG1:AI7"/>
-    <mergeCell ref="AJ1:AL7"/>
+  <mergeCells count="79">
     <mergeCell ref="A47:L47"/>
     <mergeCell ref="AM7:FA7"/>
     <mergeCell ref="AM2:FA2"/>
@@ -10565,6 +10612,12 @@
     <mergeCell ref="AB37:AB38"/>
     <mergeCell ref="AC37:AD38"/>
     <mergeCell ref="X37:AA38"/>
+    <mergeCell ref="AD1:AF2"/>
+    <mergeCell ref="AD3:AF7"/>
+    <mergeCell ref="AG1:AI2"/>
+    <mergeCell ref="AG3:AI7"/>
+    <mergeCell ref="AJ1:AL2"/>
+    <mergeCell ref="AJ3:AL7"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -12925,13 +12978,13 @@
       <selection activeCell="AF20" sqref="AF20"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" scale="59" orientation="landscape" r:id="rId1"/>
-      <autoFilter ref="A1:AF38" xr:uid="{66FD956E-59A0-4325-905F-4BD36E06F8FF}"/>
+      <autoFilter ref="A1:AF38" xr:uid="{CD0BE47F-2DD0-4117-A15A-92FC4CD1EA8E}"/>
     </customSheetView>
     <customSheetView guid="{80990883-0F2B-4732-9D4E-566B9EEB3641}" scale="115" showPageBreaks="1" fitToPage="1" showAutoFilter="1" hiddenColumns="1" topLeftCell="B7">
       <selection activeCell="W18" sqref="W18"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" scale="60" orientation="landscape" r:id="rId2"/>
-      <autoFilter ref="A1:AF38" xr:uid="{F7634ADE-9743-43BA-ADF7-891872FE3714}"/>
+      <autoFilter ref="A1:AF38" xr:uid="{2B0C2579-83AF-4441-890D-A47C1FDDED5F}"/>
     </customSheetView>
   </customSheetViews>
   <conditionalFormatting sqref="C4:C75 E4:E75 G4:G75 I4:I75 K4:K75 M4:M75 O4:O75">
